--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996030</v>
+        <v>124996025</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>886961</v>
+        <v>887302</v>
       </c>
       <c r="R2" t="n">
-        <v>7405586</v>
+        <v>7405378</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996019</v>
+        <v>124996030</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887403</v>
+        <v>886961</v>
       </c>
       <c r="R3" t="n">
-        <v>7405342</v>
+        <v>7405586</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996023</v>
+        <v>124996029</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887216</v>
+        <v>887375</v>
       </c>
       <c r="R4" t="n">
-        <v>7405474</v>
+        <v>7405296</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996025</v>
+        <v>124996024</v>
       </c>
       <c r="B5" t="n">
         <v>79920</v>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887302</v>
+        <v>887153</v>
       </c>
       <c r="R5" t="n">
-        <v>7405378</v>
+        <v>7405447</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996024</v>
+        <v>124996026</v>
       </c>
       <c r="B6" t="n">
         <v>79920</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887153</v>
+        <v>887216</v>
       </c>
       <c r="R6" t="n">
-        <v>7405447</v>
+        <v>7405352</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996029</v>
+        <v>124996028</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887375</v>
+        <v>886961</v>
       </c>
       <c r="R7" t="n">
-        <v>7405296</v>
+        <v>7405586</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996018</v>
+        <v>124996027</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>92328</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887213</v>
+        <v>886874</v>
       </c>
       <c r="R8" t="n">
-        <v>7405529</v>
+        <v>7405553</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996028</v>
+        <v>124996019</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>886961</v>
+        <v>887403</v>
       </c>
       <c r="R9" t="n">
-        <v>7405586</v>
+        <v>7405342</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1479,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>O,5 m2</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996026</v>
+        <v>124996017</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887216</v>
+        <v>887402</v>
       </c>
       <c r="R10" t="n">
-        <v>7405352</v>
+        <v>7405363</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996027</v>
+        <v>124996021</v>
       </c>
       <c r="B11" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>886874</v>
+        <v>887077</v>
       </c>
       <c r="R11" t="n">
-        <v>7405553</v>
+        <v>7405582</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996017</v>
+        <v>124996018</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887402</v>
+        <v>887213</v>
       </c>
       <c r="R12" t="n">
-        <v>7405363</v>
+        <v>7405529</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1786,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996021</v>
+        <v>124996023</v>
       </c>
       <c r="B13" t="n">
         <v>79920</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887077</v>
+        <v>887216</v>
       </c>
       <c r="R13" t="n">
-        <v>7405582</v>
+        <v>7405474</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996025</v>
+        <v>124996024</v>
       </c>
       <c r="B2" t="n">
         <v>79920</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887302</v>
+        <v>887153</v>
       </c>
       <c r="R2" t="n">
-        <v>7405378</v>
+        <v>7405447</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996030</v>
+        <v>124996025</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886961</v>
+        <v>887302</v>
       </c>
       <c r="R3" t="n">
-        <v>7405586</v>
+        <v>7405378</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996029</v>
+        <v>124996019</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887375</v>
+        <v>887403</v>
       </c>
       <c r="R4" t="n">
-        <v>7405296</v>
+        <v>7405342</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996024</v>
+        <v>124996017</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887153</v>
+        <v>887402</v>
       </c>
       <c r="R5" t="n">
-        <v>7405447</v>
+        <v>7405363</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996026</v>
+        <v>124996027</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887216</v>
+        <v>886874</v>
       </c>
       <c r="R6" t="n">
-        <v>7405352</v>
+        <v>7405553</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996028</v>
+        <v>124996018</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>886961</v>
+        <v>887213</v>
       </c>
       <c r="R7" t="n">
-        <v>7405586</v>
+        <v>7405529</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1265,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>O,5 m2</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996027</v>
+        <v>124996023</v>
       </c>
       <c r="B8" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886874</v>
+        <v>887216</v>
       </c>
       <c r="R8" t="n">
-        <v>7405553</v>
+        <v>7405474</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996019</v>
+        <v>124996030</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887403</v>
+        <v>886961</v>
       </c>
       <c r="R9" t="n">
-        <v>7405342</v>
+        <v>7405586</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1470,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996017</v>
+        <v>124996026</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887402</v>
+        <v>887216</v>
       </c>
       <c r="R10" t="n">
-        <v>7405363</v>
+        <v>7405352</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996018</v>
+        <v>124996028</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887213</v>
+        <v>886961</v>
       </c>
       <c r="R12" t="n">
-        <v>7405529</v>
+        <v>7405586</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996023</v>
+        <v>124996029</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887216</v>
+        <v>887375</v>
       </c>
       <c r="R13" t="n">
-        <v>7405474</v>
+        <v>7405296</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996024</v>
+        <v>124996018</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887153</v>
+        <v>887213</v>
       </c>
       <c r="R2" t="n">
-        <v>7405447</v>
+        <v>7405529</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996025</v>
+        <v>124996023</v>
       </c>
       <c r="B3" t="n">
         <v>79920</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887302</v>
+        <v>887216</v>
       </c>
       <c r="R3" t="n">
-        <v>7405378</v>
+        <v>7405474</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996019</v>
+        <v>124996029</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887403</v>
+        <v>887375</v>
       </c>
       <c r="R4" t="n">
-        <v>7405342</v>
+        <v>7405296</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996027</v>
+        <v>124996025</v>
       </c>
       <c r="B6" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886874</v>
+        <v>887302</v>
       </c>
       <c r="R6" t="n">
-        <v>7405553</v>
+        <v>7405378</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996018</v>
+        <v>124996027</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>92328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887213</v>
+        <v>886874</v>
       </c>
       <c r="R7" t="n">
-        <v>7405529</v>
+        <v>7405553</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996023</v>
+        <v>124996026</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1340,7 +1335,7 @@
         <v>887216</v>
       </c>
       <c r="R8" t="n">
-        <v>7405474</v>
+        <v>7405352</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996030</v>
+        <v>124996024</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>886961</v>
+        <v>887153</v>
       </c>
       <c r="R9" t="n">
-        <v>7405586</v>
+        <v>7405447</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996026</v>
+        <v>124996028</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887216</v>
+        <v>886961</v>
       </c>
       <c r="R10" t="n">
-        <v>7405352</v>
+        <v>7405586</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996021</v>
+        <v>124996030</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887077</v>
+        <v>886961</v>
       </c>
       <c r="R11" t="n">
-        <v>7405582</v>
+        <v>7405586</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996028</v>
+        <v>124996021</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>886961</v>
+        <v>887077</v>
       </c>
       <c r="R12" t="n">
-        <v>7405586</v>
+        <v>7405582</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996029</v>
+        <v>124996019</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887375</v>
+        <v>887403</v>
       </c>
       <c r="R13" t="n">
-        <v>7405296</v>
+        <v>7405342</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996021</v>
+        <v>124996019</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887077</v>
+        <v>887403</v>
       </c>
       <c r="R12" t="n">
-        <v>7405582</v>
+        <v>7405342</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996019</v>
+        <v>124996021</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887403</v>
+        <v>887077</v>
       </c>
       <c r="R13" t="n">
-        <v>7405342</v>
+        <v>7405582</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1883,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996018</v>
+        <v>124996026</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887213</v>
+        <v>887216</v>
       </c>
       <c r="R2" t="n">
-        <v>7405529</v>
+        <v>7405352</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996023</v>
+        <v>124996017</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887216</v>
+        <v>887402</v>
       </c>
       <c r="R3" t="n">
-        <v>7405474</v>
+        <v>7405363</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996029</v>
+        <v>124996018</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887375</v>
+        <v>887213</v>
       </c>
       <c r="R4" t="n">
-        <v>7405296</v>
+        <v>7405529</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996017</v>
+        <v>124996024</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887402</v>
+        <v>887153</v>
       </c>
       <c r="R5" t="n">
-        <v>7405363</v>
+        <v>7405447</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996025</v>
+        <v>124996028</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887302</v>
+        <v>886961</v>
       </c>
       <c r="R6" t="n">
-        <v>7405378</v>
+        <v>7405586</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996027</v>
+        <v>124996019</v>
       </c>
       <c r="B7" t="n">
-        <v>92328</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>886874</v>
+        <v>887403</v>
       </c>
       <c r="R7" t="n">
-        <v>7405553</v>
+        <v>7405342</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996026</v>
+        <v>124996029</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887216</v>
+        <v>887375</v>
       </c>
       <c r="R8" t="n">
-        <v>7405352</v>
+        <v>7405296</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996024</v>
+        <v>124996025</v>
       </c>
       <c r="B9" t="n">
         <v>79920</v>
@@ -1434,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887153</v>
+        <v>887302</v>
       </c>
       <c r="R9" t="n">
-        <v>7405447</v>
+        <v>7405378</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1496,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996028</v>
+        <v>124996027</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>92328</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886961</v>
+        <v>886874</v>
       </c>
       <c r="R10" t="n">
-        <v>7405586</v>
+        <v>7405553</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1572,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996019</v>
+        <v>124996021</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887403</v>
+        <v>887077</v>
       </c>
       <c r="R12" t="n">
-        <v>7405342</v>
+        <v>7405582</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996021</v>
+        <v>124996023</v>
       </c>
       <c r="B13" t="n">
         <v>79920</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887077</v>
+        <v>887216</v>
       </c>
       <c r="R13" t="n">
-        <v>7405582</v>
+        <v>7405474</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1911,6 +1911,2989 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124763698</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>887319</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7405310</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124763691</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>887027</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7405546</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124763708</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>886733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7405541</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124763714</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>887236</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7405326</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124763700</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>887330</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7405346</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124763713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>887233</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7405518</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124763694</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>887226</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7405482</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124763720</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>887336</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7405290</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124763711</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92328</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>886862</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7405531</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124763692</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>887068</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7405559</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124763710</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>887364</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7405281</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124763697</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>887296</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7405302</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124763722</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>886581</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7405577</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124763701</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>887331</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7405379</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124763712</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>887129</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7405588</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124763690</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>886921</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7405589</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124763702</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>887322</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7405379</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124763723</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>886701</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7405694</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124763693</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>887210</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7405471</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124763699</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>887357</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7405331</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124763688</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>886873</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7405551</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124763703</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>887225</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7405332</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124763689</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>887395</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7405330</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124763707</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>886642</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7405566</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124763695</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>887216</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7405484</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124763704</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>887243</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7405321</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124763715</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>886673</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7405478</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124763716</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>887420</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7405309</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124763718</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>887282</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7405303</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996017</v>
+        <v>124996029</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887402</v>
+        <v>887375</v>
       </c>
       <c r="R3" t="n">
-        <v>7405363</v>
+        <v>7405296</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996018</v>
+        <v>124996019</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887213</v>
+        <v>887403</v>
       </c>
       <c r="R4" t="n">
-        <v>7405529</v>
+        <v>7405342</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996024</v>
+        <v>124996021</v>
       </c>
       <c r="B5" t="n">
         <v>79920</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887153</v>
+        <v>887077</v>
       </c>
       <c r="R5" t="n">
-        <v>7405447</v>
+        <v>7405582</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996019</v>
+        <v>124996025</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887403</v>
+        <v>887302</v>
       </c>
       <c r="R7" t="n">
-        <v>7405342</v>
+        <v>7405378</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1271,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996029</v>
+        <v>124996027</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>92328</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887375</v>
+        <v>886874</v>
       </c>
       <c r="R8" t="n">
-        <v>7405296</v>
+        <v>7405553</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996025</v>
+        <v>124996018</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887302</v>
+        <v>887213</v>
       </c>
       <c r="R9" t="n">
-        <v>7405378</v>
+        <v>7405529</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996027</v>
+        <v>124996030</v>
       </c>
       <c r="B10" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886874</v>
+        <v>886961</v>
       </c>
       <c r="R10" t="n">
-        <v>7405553</v>
+        <v>7405586</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996030</v>
+        <v>124996023</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>886961</v>
+        <v>887216</v>
       </c>
       <c r="R11" t="n">
-        <v>7405586</v>
+        <v>7405474</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996021</v>
+        <v>124996024</v>
       </c>
       <c r="B12" t="n">
         <v>79920</v>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887077</v>
+        <v>887153</v>
       </c>
       <c r="R12" t="n">
-        <v>7405582</v>
+        <v>7405447</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996023</v>
+        <v>124996017</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887216</v>
+        <v>887402</v>
       </c>
       <c r="R13" t="n">
-        <v>7405474</v>
+        <v>7405363</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763698</v>
+        <v>124763697</v>
       </c>
       <c r="B14" t="n">
         <v>79920</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887319</v>
+        <v>887296</v>
       </c>
       <c r="R14" t="n">
-        <v>7405310</v>
+        <v>7405302</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763691</v>
+        <v>124763700</v>
       </c>
       <c r="B15" t="n">
         <v>79920</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887027</v>
+        <v>887330</v>
       </c>
       <c r="R15" t="n">
-        <v>7405546</v>
+        <v>7405346</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763708</v>
+        <v>124763704</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886733</v>
+        <v>887243</v>
       </c>
       <c r="R16" t="n">
-        <v>7405541</v>
+        <v>7405321</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763714</v>
+        <v>124763699</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887236</v>
+        <v>887357</v>
       </c>
       <c r="R17" t="n">
-        <v>7405326</v>
+        <v>7405331</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763700</v>
+        <v>124763717</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887330</v>
+        <v>886624</v>
       </c>
       <c r="R18" t="n">
-        <v>7405346</v>
+        <v>7405597</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763713</v>
+        <v>124763703</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,42 +2436,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887233</v>
+        <v>887225</v>
       </c>
       <c r="R19" t="n">
-        <v>7405518</v>
+        <v>7405332</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2517,7 +2508,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2536,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763694</v>
+        <v>124763702</v>
       </c>
       <c r="B20" t="n">
         <v>79920</v>
@@ -2576,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887226</v>
+        <v>887322</v>
       </c>
       <c r="R20" t="n">
-        <v>7405482</v>
+        <v>7405379</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2638,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763720</v>
+        <v>124763698</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887336</v>
+        <v>887319</v>
       </c>
       <c r="R21" t="n">
-        <v>7405290</v>
+        <v>7405310</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2740,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763711</v>
+        <v>124763707</v>
       </c>
       <c r="B22" t="n">
-        <v>92328</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886862</v>
+        <v>886642</v>
       </c>
       <c r="R22" t="n">
-        <v>7405531</v>
+        <v>7405566</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2816,6 +2806,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763692</v>
+        <v>124763690</v>
       </c>
       <c r="B23" t="n">
         <v>79920</v>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887068</v>
+        <v>886921</v>
       </c>
       <c r="R23" t="n">
-        <v>7405559</v>
+        <v>7405589</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2944,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763710</v>
+        <v>124763711</v>
       </c>
       <c r="B24" t="n">
-        <v>79795</v>
+        <v>92328</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887364</v>
+        <v>886862</v>
       </c>
       <c r="R24" t="n">
-        <v>7405281</v>
+        <v>7405531</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763697</v>
+        <v>124763714</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3053,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887296</v>
+        <v>887236</v>
       </c>
       <c r="R25" t="n">
-        <v>7405302</v>
+        <v>7405326</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763722</v>
+        <v>124763695</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>886581</v>
+        <v>887216</v>
       </c>
       <c r="R26" t="n">
-        <v>7405577</v>
+        <v>7405484</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763701</v>
+        <v>124763722</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3261,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887331</v>
+        <v>886581</v>
       </c>
       <c r="R27" t="n">
-        <v>7405379</v>
+        <v>7405577</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763712</v>
+        <v>124763718</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887129</v>
+        <v>887282</v>
       </c>
       <c r="R28" t="n">
-        <v>7405588</v>
+        <v>7405303</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3454,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763690</v>
+        <v>124763708</v>
       </c>
       <c r="B29" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886921</v>
+        <v>886733</v>
       </c>
       <c r="R29" t="n">
-        <v>7405589</v>
+        <v>7405541</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3530,6 +3525,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763702</v>
+        <v>124763693</v>
       </c>
       <c r="B30" t="n">
         <v>79920</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887322</v>
+        <v>887210</v>
       </c>
       <c r="R30" t="n">
-        <v>7405379</v>
+        <v>7405471</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763723</v>
+        <v>124763694</v>
       </c>
       <c r="B31" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>886701</v>
+        <v>887226</v>
       </c>
       <c r="R31" t="n">
-        <v>7405694</v>
+        <v>7405482</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763693</v>
+        <v>124763692</v>
       </c>
       <c r="B32" t="n">
         <v>79920</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887210</v>
+        <v>887068</v>
       </c>
       <c r="R32" t="n">
-        <v>7405471</v>
+        <v>7405559</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763699</v>
+        <v>124763688</v>
       </c>
       <c r="B33" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887357</v>
+        <v>886873</v>
       </c>
       <c r="R33" t="n">
-        <v>7405331</v>
+        <v>7405551</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3938,6 +3938,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3964,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763688</v>
+        <v>124763712</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3981,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886873</v>
+        <v>887129</v>
       </c>
       <c r="R34" t="n">
-        <v>7405551</v>
+        <v>7405588</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4040,11 +4045,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763703</v>
+        <v>124763715</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,25 +4083,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887225</v>
+        <v>886673</v>
       </c>
       <c r="R35" t="n">
-        <v>7405332</v>
+        <v>7405478</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763689</v>
+        <v>124763716</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887395</v>
+        <v>887420</v>
       </c>
       <c r="R36" t="n">
-        <v>7405330</v>
+        <v>7405309</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4249,11 +4249,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4280,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763707</v>
+        <v>124763689</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,25 +4287,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>886642</v>
+        <v>887395</v>
       </c>
       <c r="R37" t="n">
-        <v>7405566</v>
+        <v>7405330</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4360,7 +4355,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4387,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763695</v>
+        <v>124763723</v>
       </c>
       <c r="B38" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4403,21 +4398,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887216</v>
+        <v>886701</v>
       </c>
       <c r="R38" t="n">
-        <v>7405484</v>
+        <v>7405694</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4489,7 +4484,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763704</v>
+        <v>124763691</v>
       </c>
       <c r="B39" t="n">
         <v>79920</v>
@@ -4529,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887243</v>
+        <v>887027</v>
       </c>
       <c r="R39" t="n">
-        <v>7405321</v>
+        <v>7405546</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4591,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763715</v>
+        <v>124763719</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>886673</v>
+        <v>887305</v>
       </c>
       <c r="R40" t="n">
-        <v>7405478</v>
+        <v>7405302</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4693,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763716</v>
+        <v>124763713</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,38 +4700,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887420</v>
+        <v>887233</v>
       </c>
       <c r="R41" t="n">
-        <v>7405309</v>
+        <v>7405518</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4777,6 +4776,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763718</v>
+        <v>124763720</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887282</v>
+        <v>887336</v>
       </c>
       <c r="R42" t="n">
-        <v>7405303</v>
+        <v>7405290</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4894,6 +4894,210 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124763710</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>887364</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7405281</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124763701</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>887331</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7405379</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996021</v>
+        <v>124996028</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887077</v>
+        <v>886961</v>
       </c>
       <c r="R5" t="n">
-        <v>7405582</v>
+        <v>7405586</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996028</v>
+        <v>124996021</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886961</v>
+        <v>887077</v>
       </c>
       <c r="R6" t="n">
-        <v>7405586</v>
+        <v>7405582</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763708</v>
+        <v>124763693</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886733</v>
+        <v>887210</v>
       </c>
       <c r="R29" t="n">
-        <v>7405541</v>
+        <v>7405471</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3525,11 +3525,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763693</v>
+        <v>124763708</v>
       </c>
       <c r="B30" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3563,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887210</v>
+        <v>886733</v>
       </c>
       <c r="R30" t="n">
-        <v>7405471</v>
+        <v>7405541</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3632,6 +3627,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763712</v>
+        <v>124763715</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887129</v>
+        <v>886673</v>
       </c>
       <c r="R34" t="n">
-        <v>7405588</v>
+        <v>7405478</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763715</v>
+        <v>124763716</v>
       </c>
       <c r="B35" t="n">
         <v>91030</v>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>886673</v>
+        <v>887420</v>
       </c>
       <c r="R35" t="n">
-        <v>7405478</v>
+        <v>7405309</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763716</v>
+        <v>124763689</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887420</v>
+        <v>887395</v>
       </c>
       <c r="R36" t="n">
-        <v>7405309</v>
+        <v>7405330</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4249,6 +4249,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4275,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763689</v>
+        <v>124763712</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,25 +4292,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887395</v>
+        <v>887129</v>
       </c>
       <c r="R37" t="n">
-        <v>7405330</v>
+        <v>7405588</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4351,11 +4356,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996026</v>
+        <v>124996019</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887216</v>
+        <v>887403</v>
       </c>
       <c r="R2" t="n">
-        <v>7405352</v>
+        <v>7405342</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996029</v>
+        <v>124996027</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887375</v>
+        <v>886874</v>
       </c>
       <c r="R3" t="n">
-        <v>7405296</v>
+        <v>7405553</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996019</v>
+        <v>124996023</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887403</v>
+        <v>887216</v>
       </c>
       <c r="R4" t="n">
-        <v>7405342</v>
+        <v>7405474</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996028</v>
+        <v>124996026</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>886961</v>
+        <v>887216</v>
       </c>
       <c r="R5" t="n">
-        <v>7405586</v>
+        <v>7405352</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996021</v>
+        <v>124996029</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887077</v>
+        <v>887375</v>
       </c>
       <c r="R6" t="n">
-        <v>7405582</v>
+        <v>7405296</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996025</v>
+        <v>124996030</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887302</v>
+        <v>886961</v>
       </c>
       <c r="R7" t="n">
-        <v>7405378</v>
+        <v>7405586</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996027</v>
+        <v>124996025</v>
       </c>
       <c r="B8" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886874</v>
+        <v>887302</v>
       </c>
       <c r="R8" t="n">
-        <v>7405553</v>
+        <v>7405378</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996030</v>
+        <v>124996024</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886961</v>
+        <v>887153</v>
       </c>
       <c r="R10" t="n">
-        <v>7405586</v>
+        <v>7405447</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996023</v>
+        <v>124996028</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887216</v>
+        <v>886961</v>
       </c>
       <c r="R11" t="n">
-        <v>7405474</v>
+        <v>7405586</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1684,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996024</v>
+        <v>124996021</v>
       </c>
       <c r="B12" t="n">
         <v>79920</v>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887153</v>
+        <v>887077</v>
       </c>
       <c r="R12" t="n">
-        <v>7405447</v>
+        <v>7405582</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763697</v>
+        <v>124763719</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887296</v>
+        <v>887305</v>
       </c>
       <c r="R14" t="n">
         <v>7405302</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763700</v>
+        <v>124763699</v>
       </c>
       <c r="B15" t="n">
         <v>79920</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887330</v>
+        <v>887357</v>
       </c>
       <c r="R15" t="n">
-        <v>7405346</v>
+        <v>7405331</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763704</v>
+        <v>124763722</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887243</v>
+        <v>886581</v>
       </c>
       <c r="R16" t="n">
-        <v>7405321</v>
+        <v>7405577</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763699</v>
+        <v>124763704</v>
       </c>
       <c r="B17" t="n">
         <v>79920</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887357</v>
+        <v>887243</v>
       </c>
       <c r="R17" t="n">
-        <v>7405331</v>
+        <v>7405321</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763717</v>
+        <v>124763697</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886624</v>
+        <v>887296</v>
       </c>
       <c r="R18" t="n">
-        <v>7405597</v>
+        <v>7405302</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763703</v>
+        <v>124763701</v>
       </c>
       <c r="B19" t="n">
         <v>79920</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887225</v>
+        <v>887331</v>
       </c>
       <c r="R19" t="n">
-        <v>7405332</v>
+        <v>7405379</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763702</v>
+        <v>124763695</v>
       </c>
       <c r="B20" t="n">
         <v>79920</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887322</v>
+        <v>887216</v>
       </c>
       <c r="R20" t="n">
-        <v>7405379</v>
+        <v>7405484</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763698</v>
+        <v>124763716</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887319</v>
+        <v>887420</v>
       </c>
       <c r="R21" t="n">
-        <v>7405310</v>
+        <v>7405309</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763707</v>
+        <v>124763698</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2742,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886642</v>
+        <v>887319</v>
       </c>
       <c r="R22" t="n">
-        <v>7405566</v>
+        <v>7405310</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2806,11 +2806,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763690</v>
+        <v>124763717</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2844,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886921</v>
+        <v>886624</v>
       </c>
       <c r="R23" t="n">
-        <v>7405589</v>
+        <v>7405597</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763711</v>
+        <v>124763708</v>
       </c>
       <c r="B24" t="n">
-        <v>92328</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886862</v>
+        <v>886733</v>
       </c>
       <c r="R24" t="n">
-        <v>7405531</v>
+        <v>7405541</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3015,6 +3010,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763714</v>
+        <v>124763711</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>92328</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3053,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887236</v>
+        <v>886862</v>
       </c>
       <c r="R25" t="n">
-        <v>7405326</v>
+        <v>7405531</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763695</v>
+        <v>124763712</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887216</v>
+        <v>887129</v>
       </c>
       <c r="R26" t="n">
-        <v>7405484</v>
+        <v>7405588</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763722</v>
+        <v>124763688</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>886581</v>
+        <v>886873</v>
       </c>
       <c r="R27" t="n">
-        <v>7405577</v>
+        <v>7405551</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3321,6 +3321,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763718</v>
+        <v>124763691</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887282</v>
+        <v>887027</v>
       </c>
       <c r="R28" t="n">
-        <v>7405303</v>
+        <v>7405546</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3449,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763693</v>
+        <v>124763710</v>
       </c>
       <c r="B29" t="n">
-        <v>79920</v>
+        <v>79795</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887210</v>
+        <v>887364</v>
       </c>
       <c r="R29" t="n">
-        <v>7405471</v>
+        <v>7405281</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3551,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763708</v>
+        <v>124763718</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>886733</v>
+        <v>887282</v>
       </c>
       <c r="R30" t="n">
-        <v>7405541</v>
+        <v>7405303</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3627,11 +3632,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763694</v>
+        <v>124763720</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887226</v>
+        <v>887336</v>
       </c>
       <c r="R31" t="n">
-        <v>7405482</v>
+        <v>7405290</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763692</v>
+        <v>124763689</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887068</v>
+        <v>887395</v>
       </c>
       <c r="R32" t="n">
-        <v>7405559</v>
+        <v>7405330</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3836,6 +3836,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3862,10 +3867,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763688</v>
+        <v>124763700</v>
       </c>
       <c r="B33" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,21 +3883,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3907,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>886873</v>
+        <v>887330</v>
       </c>
       <c r="R33" t="n">
-        <v>7405551</v>
+        <v>7405346</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3938,11 +3943,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763715</v>
+        <v>124763723</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>92293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886673</v>
+        <v>886701</v>
       </c>
       <c r="R34" t="n">
-        <v>7405478</v>
+        <v>7405694</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763716</v>
+        <v>124763694</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,25 +4083,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887420</v>
+        <v>887226</v>
       </c>
       <c r="R35" t="n">
-        <v>7405309</v>
+        <v>7405482</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763689</v>
+        <v>124763715</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887395</v>
+        <v>886673</v>
       </c>
       <c r="R36" t="n">
-        <v>7405330</v>
+        <v>7405478</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4249,11 +4249,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4280,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763712</v>
+        <v>124763703</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,25 +4287,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887129</v>
+        <v>887225</v>
       </c>
       <c r="R37" t="n">
-        <v>7405588</v>
+        <v>7405332</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4382,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763723</v>
+        <v>124763702</v>
       </c>
       <c r="B38" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,21 +4393,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>886701</v>
+        <v>887322</v>
       </c>
       <c r="R38" t="n">
-        <v>7405694</v>
+        <v>7405379</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4484,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763691</v>
+        <v>124763714</v>
       </c>
       <c r="B39" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4496,25 +4491,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887027</v>
+        <v>887236</v>
       </c>
       <c r="R39" t="n">
-        <v>7405546</v>
+        <v>7405326</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4586,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763719</v>
+        <v>124763713</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,38 +4593,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887305</v>
+        <v>887233</v>
       </c>
       <c r="R40" t="n">
-        <v>7405302</v>
+        <v>7405518</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4670,6 +4669,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763713</v>
+        <v>124763692</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,42 +4700,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887233</v>
+        <v>887068</v>
       </c>
       <c r="R41" t="n">
-        <v>7405518</v>
+        <v>7405559</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4776,7 +4772,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4795,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763720</v>
+        <v>124763707</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,21 +4806,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887336</v>
+        <v>886642</v>
       </c>
       <c r="R42" t="n">
-        <v>7405290</v>
+        <v>7405566</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4871,6 +4866,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763710</v>
+        <v>124763690</v>
       </c>
       <c r="B43" t="n">
-        <v>79795</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887364</v>
+        <v>886921</v>
       </c>
       <c r="R43" t="n">
-        <v>7405281</v>
+        <v>7405589</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763701</v>
+        <v>124763693</v>
       </c>
       <c r="B44" t="n">
         <v>79920</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887331</v>
+        <v>887210</v>
       </c>
       <c r="R44" t="n">
-        <v>7405379</v>
+        <v>7405471</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996019</v>
+        <v>124996025</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887403</v>
+        <v>887302</v>
       </c>
       <c r="R2" t="n">
-        <v>7405342</v>
+        <v>7405378</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996027</v>
+        <v>124996026</v>
       </c>
       <c r="B3" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886874</v>
+        <v>887216</v>
       </c>
       <c r="R3" t="n">
-        <v>7405553</v>
+        <v>7405352</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996023</v>
+        <v>124996021</v>
       </c>
       <c r="B4" t="n">
         <v>79920</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887216</v>
+        <v>887077</v>
       </c>
       <c r="R4" t="n">
-        <v>7405474</v>
+        <v>7405582</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996026</v>
+        <v>124996027</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887216</v>
+        <v>886874</v>
       </c>
       <c r="R5" t="n">
-        <v>7405352</v>
+        <v>7405553</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996029</v>
+        <v>124996017</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887375</v>
+        <v>887402</v>
       </c>
       <c r="R6" t="n">
-        <v>7405296</v>
+        <v>7405363</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996030</v>
+        <v>124996024</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>886961</v>
+        <v>887153</v>
       </c>
       <c r="R7" t="n">
-        <v>7405586</v>
+        <v>7405447</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996025</v>
+        <v>124996030</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887302</v>
+        <v>886961</v>
       </c>
       <c r="R8" t="n">
-        <v>7405378</v>
+        <v>7405586</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996018</v>
+        <v>124996023</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887213</v>
+        <v>887216</v>
       </c>
       <c r="R9" t="n">
-        <v>7405529</v>
+        <v>7405474</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1470,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996024</v>
+        <v>124996029</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887153</v>
+        <v>887375</v>
       </c>
       <c r="R10" t="n">
-        <v>7405447</v>
+        <v>7405296</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996028</v>
+        <v>124996019</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>886961</v>
+        <v>887403</v>
       </c>
       <c r="R11" t="n">
-        <v>7405586</v>
+        <v>7405342</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1683,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>O,5 m2</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996021</v>
+        <v>124996018</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887077</v>
+        <v>887213</v>
       </c>
       <c r="R12" t="n">
-        <v>7405582</v>
+        <v>7405529</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1786,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996017</v>
+        <v>124996028</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887402</v>
+        <v>886961</v>
       </c>
       <c r="R13" t="n">
-        <v>7405363</v>
+        <v>7405586</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763699</v>
+        <v>124763714</v>
       </c>
       <c r="B15" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887357</v>
+        <v>887236</v>
       </c>
       <c r="R15" t="n">
-        <v>7405331</v>
+        <v>7405326</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763722</v>
+        <v>124763688</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886581</v>
+        <v>886873</v>
       </c>
       <c r="R16" t="n">
-        <v>7405577</v>
+        <v>7405551</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763697</v>
+        <v>124763720</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887296</v>
+        <v>887336</v>
       </c>
       <c r="R18" t="n">
-        <v>7405302</v>
+        <v>7405290</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763701</v>
+        <v>124763723</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887331</v>
+        <v>886701</v>
       </c>
       <c r="R19" t="n">
-        <v>7405379</v>
+        <v>7405694</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763695</v>
+        <v>124763708</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2543,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887216</v>
+        <v>886733</v>
       </c>
       <c r="R20" t="n">
-        <v>7405484</v>
+        <v>7405541</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2602,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2628,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763716</v>
+        <v>124763693</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887420</v>
+        <v>887210</v>
       </c>
       <c r="R21" t="n">
-        <v>7405309</v>
+        <v>7405471</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2730,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763698</v>
+        <v>124763699</v>
       </c>
       <c r="B22" t="n">
         <v>79920</v>
@@ -2770,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887319</v>
+        <v>887357</v>
       </c>
       <c r="R22" t="n">
-        <v>7405310</v>
+        <v>7405331</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2832,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763717</v>
+        <v>124763692</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886624</v>
+        <v>887068</v>
       </c>
       <c r="R23" t="n">
-        <v>7405597</v>
+        <v>7405559</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2934,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763708</v>
+        <v>124763711</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>92328</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2950,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886733</v>
+        <v>886862</v>
       </c>
       <c r="R24" t="n">
-        <v>7405541</v>
+        <v>7405531</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3010,11 +3020,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763711</v>
+        <v>124763722</v>
       </c>
       <c r="B25" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3058,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>886862</v>
+        <v>886581</v>
       </c>
       <c r="R25" t="n">
-        <v>7405531</v>
+        <v>7405577</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763712</v>
+        <v>124763697</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887129</v>
+        <v>887296</v>
       </c>
       <c r="R26" t="n">
-        <v>7405588</v>
+        <v>7405302</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3245,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763688</v>
+        <v>124763710</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>79795</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>886873</v>
+        <v>887364</v>
       </c>
       <c r="R27" t="n">
-        <v>7405551</v>
+        <v>7405281</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3321,11 +3326,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763691</v>
+        <v>124763700</v>
       </c>
       <c r="B28" t="n">
         <v>79920</v>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887027</v>
+        <v>887330</v>
       </c>
       <c r="R28" t="n">
-        <v>7405546</v>
+        <v>7405346</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763710</v>
+        <v>124763690</v>
       </c>
       <c r="B29" t="n">
-        <v>79795</v>
+        <v>79920</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887364</v>
+        <v>886921</v>
       </c>
       <c r="R29" t="n">
-        <v>7405281</v>
+        <v>7405589</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763718</v>
+        <v>124763691</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887282</v>
+        <v>887027</v>
       </c>
       <c r="R30" t="n">
-        <v>7405303</v>
+        <v>7405546</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763720</v>
+        <v>124763712</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887336</v>
+        <v>887129</v>
       </c>
       <c r="R31" t="n">
-        <v>7405290</v>
+        <v>7405588</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763689</v>
+        <v>124763703</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887395</v>
+        <v>887225</v>
       </c>
       <c r="R32" t="n">
-        <v>7405330</v>
+        <v>7405332</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3836,11 +3836,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3867,7 +3862,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763700</v>
+        <v>124763698</v>
       </c>
       <c r="B33" t="n">
         <v>79920</v>
@@ -3907,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887330</v>
+        <v>887319</v>
       </c>
       <c r="R33" t="n">
-        <v>7405346</v>
+        <v>7405310</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3969,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763723</v>
+        <v>124763715</v>
       </c>
       <c r="B34" t="n">
-        <v>92293</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3981,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4009,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886701</v>
+        <v>886673</v>
       </c>
       <c r="R34" t="n">
-        <v>7405694</v>
+        <v>7405478</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4071,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763694</v>
+        <v>124763716</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887226</v>
+        <v>887420</v>
       </c>
       <c r="R35" t="n">
-        <v>7405482</v>
+        <v>7405309</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4173,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763715</v>
+        <v>124763718</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,21 +4184,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>886673</v>
+        <v>887282</v>
       </c>
       <c r="R36" t="n">
-        <v>7405478</v>
+        <v>7405303</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4275,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763703</v>
+        <v>124763717</v>
       </c>
       <c r="B37" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,25 +4282,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887225</v>
+        <v>886624</v>
       </c>
       <c r="R37" t="n">
-        <v>7405332</v>
+        <v>7405597</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4377,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763702</v>
+        <v>124763701</v>
       </c>
       <c r="B38" t="n">
         <v>79920</v>
@@ -4417,7 +4412,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887322</v>
+        <v>887331</v>
       </c>
       <c r="R38" t="n">
         <v>7405379</v>
@@ -4479,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763714</v>
+        <v>124763694</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4491,25 +4486,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887236</v>
+        <v>887226</v>
       </c>
       <c r="R39" t="n">
-        <v>7405326</v>
+        <v>7405482</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4581,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763713</v>
+        <v>124763702</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4593,42 +4588,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887233</v>
+        <v>887322</v>
       </c>
       <c r="R40" t="n">
-        <v>7405518</v>
+        <v>7405379</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4669,7 +4660,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4688,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763692</v>
+        <v>124763689</v>
       </c>
       <c r="B41" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,21 +4694,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887068</v>
+        <v>887395</v>
       </c>
       <c r="R41" t="n">
-        <v>7405559</v>
+        <v>7405330</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4764,6 +4754,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4790,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763707</v>
+        <v>124763713</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4802,38 +4797,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>886642</v>
+        <v>887233</v>
       </c>
       <c r="R42" t="n">
-        <v>7405566</v>
+        <v>7405518</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4868,17 +4867,13 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4897,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763690</v>
+        <v>124763707</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,25 +4904,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>886921</v>
+        <v>886642</v>
       </c>
       <c r="R43" t="n">
-        <v>7405589</v>
+        <v>7405566</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4973,6 +4968,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4999,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763693</v>
+        <v>124763695</v>
       </c>
       <c r="B44" t="n">
         <v>79920</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887210</v>
+        <v>887216</v>
       </c>
       <c r="R44" t="n">
-        <v>7405471</v>
+        <v>7405484</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996026</v>
+        <v>124996030</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887216</v>
+        <v>886961</v>
       </c>
       <c r="R3" t="n">
-        <v>7405352</v>
+        <v>7405586</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996021</v>
+        <v>124996027</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887077</v>
+        <v>886874</v>
       </c>
       <c r="R4" t="n">
-        <v>7405582</v>
+        <v>7405553</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996027</v>
+        <v>124996019</v>
       </c>
       <c r="B5" t="n">
-        <v>92328</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>886874</v>
+        <v>887403</v>
       </c>
       <c r="R5" t="n">
-        <v>7405553</v>
+        <v>7405342</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996024</v>
+        <v>124996028</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887153</v>
+        <v>886961</v>
       </c>
       <c r="R7" t="n">
-        <v>7405447</v>
+        <v>7405586</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996030</v>
+        <v>124996026</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886961</v>
+        <v>887216</v>
       </c>
       <c r="R8" t="n">
-        <v>7405586</v>
+        <v>7405352</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996023</v>
+        <v>124996021</v>
       </c>
       <c r="B9" t="n">
         <v>79920</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887216</v>
+        <v>887077</v>
       </c>
       <c r="R9" t="n">
-        <v>7405474</v>
+        <v>7405582</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996029</v>
+        <v>124996024</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887375</v>
+        <v>887153</v>
       </c>
       <c r="R10" t="n">
-        <v>7405296</v>
+        <v>7405447</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996019</v>
+        <v>124996029</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887403</v>
+        <v>887375</v>
       </c>
       <c r="R11" t="n">
-        <v>7405342</v>
+        <v>7405296</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1669,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996018</v>
+        <v>124996023</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887213</v>
+        <v>887216</v>
       </c>
       <c r="R12" t="n">
-        <v>7405529</v>
+        <v>7405474</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996028</v>
+        <v>124996018</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>886961</v>
+        <v>887213</v>
       </c>
       <c r="R13" t="n">
-        <v>7405586</v>
+        <v>7405529</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>O,5 m2</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763719</v>
+        <v>124763718</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887305</v>
+        <v>887282</v>
       </c>
       <c r="R14" t="n">
-        <v>7405302</v>
+        <v>7405303</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763714</v>
+        <v>124763717</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887236</v>
+        <v>886624</v>
       </c>
       <c r="R15" t="n">
-        <v>7405326</v>
+        <v>7405597</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763688</v>
+        <v>124763690</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886873</v>
+        <v>886921</v>
       </c>
       <c r="R16" t="n">
-        <v>7405551</v>
+        <v>7405589</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763704</v>
+        <v>124763689</v>
       </c>
       <c r="B17" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887243</v>
+        <v>887395</v>
       </c>
       <c r="R17" t="n">
-        <v>7405321</v>
+        <v>7405330</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2301,6 +2296,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763720</v>
+        <v>124763692</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887336</v>
+        <v>887068</v>
       </c>
       <c r="R18" t="n">
-        <v>7405290</v>
+        <v>7405559</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763723</v>
+        <v>124763703</v>
       </c>
       <c r="B19" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>886701</v>
+        <v>887225</v>
       </c>
       <c r="R19" t="n">
-        <v>7405694</v>
+        <v>7405332</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763708</v>
+        <v>124763704</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2543,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886733</v>
+        <v>887243</v>
       </c>
       <c r="R20" t="n">
-        <v>7405541</v>
+        <v>7405321</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2607,11 +2607,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763693</v>
+        <v>124763699</v>
       </c>
       <c r="B21" t="n">
         <v>79920</v>
@@ -2678,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887210</v>
+        <v>887357</v>
       </c>
       <c r="R21" t="n">
-        <v>7405471</v>
+        <v>7405331</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2740,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763699</v>
+        <v>124763702</v>
       </c>
       <c r="B22" t="n">
         <v>79920</v>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887357</v>
+        <v>887322</v>
       </c>
       <c r="R22" t="n">
-        <v>7405331</v>
+        <v>7405379</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763692</v>
+        <v>124763716</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887068</v>
+        <v>887420</v>
       </c>
       <c r="R23" t="n">
-        <v>7405559</v>
+        <v>7405309</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2944,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763711</v>
+        <v>124763698</v>
       </c>
       <c r="B24" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886862</v>
+        <v>887319</v>
       </c>
       <c r="R24" t="n">
-        <v>7405531</v>
+        <v>7405310</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763722</v>
+        <v>124763701</v>
       </c>
       <c r="B25" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>886581</v>
+        <v>887331</v>
       </c>
       <c r="R25" t="n">
-        <v>7405577</v>
+        <v>7405379</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763697</v>
+        <v>124763715</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887296</v>
+        <v>886673</v>
       </c>
       <c r="R26" t="n">
-        <v>7405302</v>
+        <v>7405478</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763710</v>
+        <v>124763714</v>
       </c>
       <c r="B27" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887364</v>
+        <v>887236</v>
       </c>
       <c r="R27" t="n">
-        <v>7405281</v>
+        <v>7405326</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763700</v>
+        <v>124763720</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887330</v>
+        <v>887336</v>
       </c>
       <c r="R28" t="n">
-        <v>7405346</v>
+        <v>7405290</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3454,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763690</v>
+        <v>124763711</v>
       </c>
       <c r="B29" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886921</v>
+        <v>886862</v>
       </c>
       <c r="R29" t="n">
-        <v>7405589</v>
+        <v>7405531</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3556,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763691</v>
+        <v>124763708</v>
       </c>
       <c r="B30" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3563,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887027</v>
+        <v>886733</v>
       </c>
       <c r="R30" t="n">
-        <v>7405546</v>
+        <v>7405541</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3632,6 +3627,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763712</v>
+        <v>124763694</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887129</v>
+        <v>887226</v>
       </c>
       <c r="R31" t="n">
-        <v>7405588</v>
+        <v>7405482</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763703</v>
+        <v>124763710</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>79795</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887225</v>
+        <v>887364</v>
       </c>
       <c r="R32" t="n">
-        <v>7405332</v>
+        <v>7405281</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763698</v>
+        <v>124763712</v>
       </c>
       <c r="B33" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887319</v>
+        <v>887129</v>
       </c>
       <c r="R33" t="n">
-        <v>7405310</v>
+        <v>7405588</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763715</v>
+        <v>124763713</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,38 +3976,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886673</v>
+        <v>887233</v>
       </c>
       <c r="R34" t="n">
-        <v>7405478</v>
+        <v>7405518</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4048,6 +4052,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4066,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763716</v>
+        <v>124763719</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,21 +4087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887420</v>
+        <v>887305</v>
       </c>
       <c r="R35" t="n">
-        <v>7405309</v>
+        <v>7405302</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4168,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763718</v>
+        <v>124763691</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4180,25 +4185,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887282</v>
+        <v>887027</v>
       </c>
       <c r="R36" t="n">
-        <v>7405303</v>
+        <v>7405546</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4270,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763717</v>
+        <v>124763722</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4282,25 +4287,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4310,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>886624</v>
+        <v>886581</v>
       </c>
       <c r="R37" t="n">
-        <v>7405597</v>
+        <v>7405577</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4372,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763701</v>
+        <v>124763707</v>
       </c>
       <c r="B38" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4389,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887331</v>
+        <v>886642</v>
       </c>
       <c r="R38" t="n">
-        <v>7405379</v>
+        <v>7405566</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4448,6 +4453,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4474,7 +4484,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763694</v>
+        <v>124763700</v>
       </c>
       <c r="B39" t="n">
         <v>79920</v>
@@ -4514,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887226</v>
+        <v>887330</v>
       </c>
       <c r="R39" t="n">
-        <v>7405482</v>
+        <v>7405346</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4576,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763702</v>
+        <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887322</v>
+        <v>886873</v>
       </c>
       <c r="R40" t="n">
-        <v>7405379</v>
+        <v>7405551</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4652,6 +4662,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4678,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763689</v>
+        <v>124763723</v>
       </c>
       <c r="B41" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,21 +4709,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887395</v>
+        <v>886701</v>
       </c>
       <c r="R41" t="n">
-        <v>7405330</v>
+        <v>7405694</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4754,11 +4769,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4785,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763713</v>
+        <v>124763697</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4797,42 +4807,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887233</v>
+        <v>887296</v>
       </c>
       <c r="R42" t="n">
-        <v>7405518</v>
+        <v>7405302</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4873,7 +4879,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4892,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763707</v>
+        <v>124763695</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4904,25 +4909,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>886642</v>
+        <v>887216</v>
       </c>
       <c r="R43" t="n">
-        <v>7405566</v>
+        <v>7405484</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4968,11 +4973,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4999,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763695</v>
+        <v>124763693</v>
       </c>
       <c r="B44" t="n">
         <v>79920</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887216</v>
+        <v>887210</v>
       </c>
       <c r="R44" t="n">
-        <v>7405484</v>
+        <v>7405471</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996017</v>
+        <v>124996028</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887402</v>
+        <v>886961</v>
       </c>
       <c r="R6" t="n">
-        <v>7405363</v>
+        <v>7405586</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996028</v>
+        <v>124996017</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>886961</v>
+        <v>887402</v>
       </c>
       <c r="R7" t="n">
-        <v>7405586</v>
+        <v>7405363</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763718</v>
+        <v>124763717</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887282</v>
+        <v>886624</v>
       </c>
       <c r="R14" t="n">
-        <v>7405303</v>
+        <v>7405597</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763717</v>
+        <v>124763718</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>886624</v>
+        <v>887282</v>
       </c>
       <c r="R15" t="n">
-        <v>7405597</v>
+        <v>7405303</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996025</v>
+        <v>124996018</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887302</v>
+        <v>887213</v>
       </c>
       <c r="R2" t="n">
-        <v>7405378</v>
+        <v>7405529</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996030</v>
+        <v>124996024</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886961</v>
+        <v>887153</v>
       </c>
       <c r="R3" t="n">
-        <v>7405586</v>
+        <v>7405447</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996027</v>
+        <v>124996021</v>
       </c>
       <c r="B4" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>886874</v>
+        <v>887077</v>
       </c>
       <c r="R4" t="n">
-        <v>7405553</v>
+        <v>7405582</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996028</v>
+        <v>124996029</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>886961</v>
+        <v>887375</v>
       </c>
       <c r="R6" t="n">
-        <v>7405586</v>
+        <v>7405296</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996017</v>
+        <v>124996026</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887402</v>
+        <v>887216</v>
       </c>
       <c r="R7" t="n">
-        <v>7405363</v>
+        <v>7405352</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996026</v>
+        <v>124996025</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887216</v>
+        <v>887302</v>
       </c>
       <c r="R8" t="n">
-        <v>7405352</v>
+        <v>7405378</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996021</v>
+        <v>124996027</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887077</v>
+        <v>886874</v>
       </c>
       <c r="R9" t="n">
-        <v>7405582</v>
+        <v>7405553</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996024</v>
+        <v>124996030</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887153</v>
+        <v>886961</v>
       </c>
       <c r="R10" t="n">
-        <v>7405447</v>
+        <v>7405586</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996029</v>
+        <v>124996017</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887375</v>
+        <v>887402</v>
       </c>
       <c r="R11" t="n">
-        <v>7405296</v>
+        <v>7405363</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996023</v>
+        <v>124996028</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887216</v>
+        <v>886961</v>
       </c>
       <c r="R12" t="n">
-        <v>7405474</v>
+        <v>7405586</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996018</v>
+        <v>124996023</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887213</v>
+        <v>887216</v>
       </c>
       <c r="R13" t="n">
-        <v>7405529</v>
+        <v>7405474</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1883,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763717</v>
+        <v>124763701</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>886624</v>
+        <v>887331</v>
       </c>
       <c r="R14" t="n">
-        <v>7405597</v>
+        <v>7405379</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763718</v>
+        <v>124763695</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887282</v>
+        <v>887216</v>
       </c>
       <c r="R15" t="n">
-        <v>7405303</v>
+        <v>7405484</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763690</v>
+        <v>124763715</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886921</v>
+        <v>886673</v>
       </c>
       <c r="R16" t="n">
-        <v>7405589</v>
+        <v>7405478</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763689</v>
+        <v>124763714</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887395</v>
+        <v>887236</v>
       </c>
       <c r="R17" t="n">
-        <v>7405330</v>
+        <v>7405326</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2296,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763692</v>
+        <v>124763688</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887068</v>
+        <v>886873</v>
       </c>
       <c r="R18" t="n">
-        <v>7405559</v>
+        <v>7405551</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2403,6 +2398,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763703</v>
+        <v>124763718</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887225</v>
+        <v>887282</v>
       </c>
       <c r="R19" t="n">
-        <v>7405332</v>
+        <v>7405303</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763704</v>
+        <v>124763690</v>
       </c>
       <c r="B20" t="n">
         <v>79920</v>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887243</v>
+        <v>886921</v>
       </c>
       <c r="R20" t="n">
-        <v>7405321</v>
+        <v>7405589</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763699</v>
+        <v>124763689</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887357</v>
+        <v>887395</v>
       </c>
       <c r="R21" t="n">
-        <v>7405331</v>
+        <v>7405330</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2709,6 +2709,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763702</v>
+        <v>124763722</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887322</v>
+        <v>886581</v>
       </c>
       <c r="R22" t="n">
-        <v>7405379</v>
+        <v>7405577</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2837,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763716</v>
+        <v>124763702</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887420</v>
+        <v>887322</v>
       </c>
       <c r="R23" t="n">
-        <v>7405309</v>
+        <v>7405379</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2939,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763698</v>
+        <v>124763707</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887319</v>
+        <v>886642</v>
       </c>
       <c r="R24" t="n">
-        <v>7405310</v>
+        <v>7405566</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3015,6 +3020,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,7 +3051,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763701</v>
+        <v>124763704</v>
       </c>
       <c r="B25" t="n">
         <v>79920</v>
@@ -3081,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887331</v>
+        <v>887243</v>
       </c>
       <c r="R25" t="n">
-        <v>7405379</v>
+        <v>7405321</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3143,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763715</v>
+        <v>124763700</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3165,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>886673</v>
+        <v>887330</v>
       </c>
       <c r="R26" t="n">
-        <v>7405478</v>
+        <v>7405346</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3245,7 +3255,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763714</v>
+        <v>124763713</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3279,16 +3289,20 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887236</v>
+        <v>887233</v>
       </c>
       <c r="R27" t="n">
-        <v>7405326</v>
+        <v>7405518</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3329,6 +3343,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3347,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763720</v>
+        <v>124763716</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3378,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887336</v>
+        <v>887420</v>
       </c>
       <c r="R28" t="n">
-        <v>7405290</v>
+        <v>7405309</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3449,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763711</v>
+        <v>124763698</v>
       </c>
       <c r="B29" t="n">
-        <v>92328</v>
+        <v>79920</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3476,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886862</v>
+        <v>887319</v>
       </c>
       <c r="R29" t="n">
-        <v>7405531</v>
+        <v>7405310</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3551,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763708</v>
+        <v>124763692</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,25 +3578,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>886733</v>
+        <v>887068</v>
       </c>
       <c r="R30" t="n">
-        <v>7405541</v>
+        <v>7405559</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3627,11 +3642,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763694</v>
+        <v>124763712</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3680,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887226</v>
+        <v>887129</v>
       </c>
       <c r="R31" t="n">
-        <v>7405482</v>
+        <v>7405588</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3862,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763712</v>
+        <v>124763711</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>92328</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3884,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887129</v>
+        <v>886862</v>
       </c>
       <c r="R33" t="n">
-        <v>7405588</v>
+        <v>7405531</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3964,10 +3974,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763713</v>
+        <v>124763723</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,42 +3986,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887233</v>
+        <v>886701</v>
       </c>
       <c r="R34" t="n">
-        <v>7405518</v>
+        <v>7405694</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4052,7 +4058,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4071,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763719</v>
+        <v>124763691</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,25 +4088,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887305</v>
+        <v>887027</v>
       </c>
       <c r="R35" t="n">
-        <v>7405302</v>
+        <v>7405546</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4173,7 +4178,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763691</v>
+        <v>124763697</v>
       </c>
       <c r="B36" t="n">
         <v>79920</v>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887027</v>
+        <v>887296</v>
       </c>
       <c r="R36" t="n">
-        <v>7405546</v>
+        <v>7405302</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4275,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763722</v>
+        <v>124763720</v>
       </c>
       <c r="B37" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,25 +4292,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>886581</v>
+        <v>887336</v>
       </c>
       <c r="R37" t="n">
-        <v>7405577</v>
+        <v>7405290</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4377,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763707</v>
+        <v>124763694</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4389,25 +4394,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>886642</v>
+        <v>887226</v>
       </c>
       <c r="R38" t="n">
-        <v>7405566</v>
+        <v>7405482</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4453,11 +4458,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4484,7 +4484,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763700</v>
+        <v>124763699</v>
       </c>
       <c r="B39" t="n">
         <v>79920</v>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887330</v>
+        <v>887357</v>
       </c>
       <c r="R39" t="n">
-        <v>7405346</v>
+        <v>7405331</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763688</v>
+        <v>124763717</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,25 +4598,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>886873</v>
+        <v>886624</v>
       </c>
       <c r="R40" t="n">
-        <v>7405551</v>
+        <v>7405597</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4662,11 +4662,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4693,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763723</v>
+        <v>124763708</v>
       </c>
       <c r="B41" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>886701</v>
+        <v>886733</v>
       </c>
       <c r="R41" t="n">
-        <v>7405694</v>
+        <v>7405541</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4769,6 +4764,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4795,7 +4795,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763697</v>
+        <v>124763703</v>
       </c>
       <c r="B42" t="n">
         <v>79920</v>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887296</v>
+        <v>887225</v>
       </c>
       <c r="R42" t="n">
-        <v>7405302</v>
+        <v>7405332</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763695</v>
+        <v>124763719</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,25 +4909,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887216</v>
+        <v>887305</v>
       </c>
       <c r="R43" t="n">
-        <v>7405484</v>
+        <v>7405302</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763695</v>
+        <v>124763715</v>
       </c>
       <c r="B15" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887216</v>
+        <v>886673</v>
       </c>
       <c r="R15" t="n">
-        <v>7405484</v>
+        <v>7405478</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763715</v>
+        <v>124763695</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886673</v>
+        <v>887216</v>
       </c>
       <c r="R16" t="n">
-        <v>7405478</v>
+        <v>7405484</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996018</v>
+        <v>124996028</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887213</v>
+        <v>886961</v>
       </c>
       <c r="R2" t="n">
-        <v>7405529</v>
+        <v>7405586</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996024</v>
+        <v>124996023</v>
       </c>
       <c r="B3" t="n">
         <v>79920</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887153</v>
+        <v>887216</v>
       </c>
       <c r="R3" t="n">
-        <v>7405447</v>
+        <v>7405474</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996021</v>
+        <v>124996025</v>
       </c>
       <c r="B4" t="n">
         <v>79920</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887077</v>
+        <v>887302</v>
       </c>
       <c r="R4" t="n">
-        <v>7405582</v>
+        <v>7405378</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996019</v>
+        <v>124996018</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887403</v>
+        <v>887213</v>
       </c>
       <c r="R5" t="n">
-        <v>7405342</v>
+        <v>7405529</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996029</v>
+        <v>124996021</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887375</v>
+        <v>887077</v>
       </c>
       <c r="R6" t="n">
-        <v>7405296</v>
+        <v>7405582</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996026</v>
+        <v>124996019</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887216</v>
+        <v>887403</v>
       </c>
       <c r="R7" t="n">
-        <v>7405352</v>
+        <v>7405342</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996025</v>
+        <v>124996027</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887302</v>
+        <v>886874</v>
       </c>
       <c r="R8" t="n">
-        <v>7405378</v>
+        <v>7405553</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996027</v>
+        <v>124996029</v>
       </c>
       <c r="B9" t="n">
-        <v>92328</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>886874</v>
+        <v>887375</v>
       </c>
       <c r="R9" t="n">
-        <v>7405553</v>
+        <v>7405296</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996030</v>
+        <v>124996024</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>886961</v>
+        <v>887153</v>
       </c>
       <c r="R10" t="n">
-        <v>7405586</v>
+        <v>7405447</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996017</v>
+        <v>124996030</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887402</v>
+        <v>886961</v>
       </c>
       <c r="R11" t="n">
-        <v>7405363</v>
+        <v>7405586</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996028</v>
+        <v>124996017</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>886961</v>
+        <v>887402</v>
       </c>
       <c r="R12" t="n">
-        <v>7405586</v>
+        <v>7405363</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996023</v>
+        <v>124996026</v>
       </c>
       <c r="B13" t="n">
         <v>79920</v>
@@ -1855,7 +1855,7 @@
         <v>887216</v>
       </c>
       <c r="R13" t="n">
-        <v>7405474</v>
+        <v>7405352</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763701</v>
+        <v>124763711</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>92328</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887331</v>
+        <v>886862</v>
       </c>
       <c r="R14" t="n">
-        <v>7405379</v>
+        <v>7405531</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763715</v>
+        <v>124763723</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>92293</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>886673</v>
+        <v>886701</v>
       </c>
       <c r="R15" t="n">
-        <v>7405478</v>
+        <v>7405694</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763695</v>
+        <v>124763707</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887216</v>
+        <v>886642</v>
       </c>
       <c r="R16" t="n">
-        <v>7405484</v>
+        <v>7405566</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763714</v>
+        <v>124763692</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887236</v>
+        <v>887068</v>
       </c>
       <c r="R17" t="n">
-        <v>7405326</v>
+        <v>7405559</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763688</v>
+        <v>124763701</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886873</v>
+        <v>887331</v>
       </c>
       <c r="R18" t="n">
-        <v>7405551</v>
+        <v>7405379</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2398,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763718</v>
+        <v>124763699</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887282</v>
+        <v>887357</v>
       </c>
       <c r="R19" t="n">
-        <v>7405303</v>
+        <v>7405331</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763690</v>
+        <v>124763717</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2543,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886921</v>
+        <v>886624</v>
       </c>
       <c r="R20" t="n">
-        <v>7405589</v>
+        <v>7405597</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763689</v>
+        <v>124763703</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887395</v>
+        <v>887225</v>
       </c>
       <c r="R21" t="n">
-        <v>7405330</v>
+        <v>7405332</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2709,11 +2709,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763722</v>
+        <v>124763690</v>
       </c>
       <c r="B22" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2756,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886581</v>
+        <v>886921</v>
       </c>
       <c r="R22" t="n">
-        <v>7405577</v>
+        <v>7405589</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763702</v>
+        <v>124763688</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887322</v>
+        <v>886873</v>
       </c>
       <c r="R23" t="n">
-        <v>7405379</v>
+        <v>7405551</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2918,6 +2913,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763707</v>
+        <v>124763689</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886642</v>
+        <v>887395</v>
       </c>
       <c r="R24" t="n">
-        <v>7405566</v>
+        <v>7405330</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763704</v>
+        <v>124763708</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,25 +3063,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887243</v>
+        <v>886733</v>
       </c>
       <c r="R25" t="n">
-        <v>7405321</v>
+        <v>7405541</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3127,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,7 +3158,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763700</v>
+        <v>124763704</v>
       </c>
       <c r="B26" t="n">
         <v>79920</v>
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887330</v>
+        <v>887243</v>
       </c>
       <c r="R26" t="n">
-        <v>7405346</v>
+        <v>7405321</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3255,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763713</v>
+        <v>124763697</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3267,42 +3272,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887233</v>
+        <v>887296</v>
       </c>
       <c r="R27" t="n">
-        <v>7405518</v>
+        <v>7405302</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3343,7 +3344,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763716</v>
+        <v>124763698</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3374,25 +3374,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887420</v>
+        <v>887319</v>
       </c>
       <c r="R28" t="n">
-        <v>7405309</v>
+        <v>7405310</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763698</v>
+        <v>124763693</v>
       </c>
       <c r="B29" t="n">
         <v>79920</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887319</v>
+        <v>887210</v>
       </c>
       <c r="R29" t="n">
-        <v>7405310</v>
+        <v>7405471</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763692</v>
+        <v>124763720</v>
       </c>
       <c r="B30" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3578,25 +3578,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887068</v>
+        <v>887336</v>
       </c>
       <c r="R30" t="n">
-        <v>7405559</v>
+        <v>7405290</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763712</v>
+        <v>124763718</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,25 +3680,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887129</v>
+        <v>887282</v>
       </c>
       <c r="R31" t="n">
-        <v>7405588</v>
+        <v>7405303</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763710</v>
+        <v>124763719</v>
       </c>
       <c r="B32" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,25 +3782,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887364</v>
+        <v>887305</v>
       </c>
       <c r="R32" t="n">
-        <v>7405281</v>
+        <v>7405302</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763711</v>
+        <v>124763713</v>
       </c>
       <c r="B33" t="n">
-        <v>92328</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3884,38 +3884,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>886862</v>
+        <v>887233</v>
       </c>
       <c r="R33" t="n">
-        <v>7405531</v>
+        <v>7405518</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3956,6 +3960,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3974,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763723</v>
+        <v>124763694</v>
       </c>
       <c r="B34" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,21 +3995,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4014,10 +4019,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886701</v>
+        <v>887226</v>
       </c>
       <c r="R34" t="n">
-        <v>7405694</v>
+        <v>7405482</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4076,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763691</v>
+        <v>124763710</v>
       </c>
       <c r="B35" t="n">
-        <v>79920</v>
+        <v>79795</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4092,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4116,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887027</v>
+        <v>887364</v>
       </c>
       <c r="R35" t="n">
-        <v>7405546</v>
+        <v>7405281</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4178,10 +4183,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763697</v>
+        <v>124763716</v>
       </c>
       <c r="B36" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4190,25 +4195,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887296</v>
+        <v>887420</v>
       </c>
       <c r="R36" t="n">
-        <v>7405302</v>
+        <v>7405309</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4280,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763720</v>
+        <v>124763702</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,25 +4297,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4325,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887336</v>
+        <v>887322</v>
       </c>
       <c r="R37" t="n">
-        <v>7405290</v>
+        <v>7405379</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4382,7 +4387,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763694</v>
+        <v>124763691</v>
       </c>
       <c r="B38" t="n">
         <v>79920</v>
@@ -4422,10 +4427,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887226</v>
+        <v>887027</v>
       </c>
       <c r="R38" t="n">
-        <v>7405482</v>
+        <v>7405546</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4484,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763699</v>
+        <v>124763715</v>
       </c>
       <c r="B39" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4496,25 +4501,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4529,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887357</v>
+        <v>886673</v>
       </c>
       <c r="R39" t="n">
-        <v>7405331</v>
+        <v>7405478</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4586,10 +4591,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763717</v>
+        <v>124763695</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,25 +4603,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>886624</v>
+        <v>887216</v>
       </c>
       <c r="R40" t="n">
-        <v>7405597</v>
+        <v>7405484</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4688,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763708</v>
+        <v>124763714</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,25 +4705,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4733,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>886733</v>
+        <v>887236</v>
       </c>
       <c r="R41" t="n">
-        <v>7405541</v>
+        <v>7405326</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4764,11 +4769,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763703</v>
+        <v>124763712</v>
       </c>
       <c r="B42" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,25 +4807,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887225</v>
+        <v>887129</v>
       </c>
       <c r="R42" t="n">
-        <v>7405332</v>
+        <v>7405588</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763719</v>
+        <v>124763700</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,25 +4909,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887305</v>
+        <v>887330</v>
       </c>
       <c r="R43" t="n">
-        <v>7405302</v>
+        <v>7405346</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763693</v>
+        <v>124763722</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887210</v>
+        <v>886581</v>
       </c>
       <c r="R44" t="n">
-        <v>7405471</v>
+        <v>7405577</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996028</v>
+        <v>124996017</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>886961</v>
+        <v>887402</v>
       </c>
       <c r="R2" t="n">
-        <v>7405586</v>
+        <v>7405363</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996023</v>
+        <v>124996019</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887216</v>
+        <v>887403</v>
       </c>
       <c r="R3" t="n">
-        <v>7405474</v>
+        <v>7405342</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996025</v>
+        <v>124996029</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887302</v>
+        <v>887375</v>
       </c>
       <c r="R4" t="n">
-        <v>7405378</v>
+        <v>7405296</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996018</v>
+        <v>124996024</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>80057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887213</v>
+        <v>887153</v>
       </c>
       <c r="R5" t="n">
-        <v>7405529</v>
+        <v>7405447</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996021</v>
+        <v>124996025</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887077</v>
+        <v>887302</v>
       </c>
       <c r="R6" t="n">
-        <v>7405582</v>
+        <v>7405378</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996019</v>
+        <v>124996027</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>92484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887403</v>
+        <v>886874</v>
       </c>
       <c r="R7" t="n">
-        <v>7405342</v>
+        <v>7405553</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1271,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996027</v>
+        <v>124996018</v>
       </c>
       <c r="B8" t="n">
-        <v>92328</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886874</v>
+        <v>887213</v>
       </c>
       <c r="R8" t="n">
-        <v>7405553</v>
+        <v>7405529</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1378,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996029</v>
+        <v>124996030</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>92448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887375</v>
+        <v>886961</v>
       </c>
       <c r="R9" t="n">
-        <v>7405296</v>
+        <v>7405586</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996024</v>
+        <v>124996026</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887153</v>
+        <v>887216</v>
       </c>
       <c r="R10" t="n">
-        <v>7405447</v>
+        <v>7405352</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996030</v>
+        <v>124996021</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>80057</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>886961</v>
+        <v>887077</v>
       </c>
       <c r="R11" t="n">
-        <v>7405586</v>
+        <v>7405582</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996017</v>
+        <v>124996028</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887402</v>
+        <v>886961</v>
       </c>
       <c r="R12" t="n">
-        <v>7405363</v>
+        <v>7405586</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1786,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996026</v>
+        <v>124996023</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>887216</v>
       </c>
       <c r="R13" t="n">
-        <v>7405352</v>
+        <v>7405474</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763711</v>
+        <v>124763704</v>
       </c>
       <c r="B14" t="n">
-        <v>92328</v>
+        <v>80057</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>886862</v>
+        <v>887243</v>
       </c>
       <c r="R14" t="n">
-        <v>7405531</v>
+        <v>7405321</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763723</v>
+        <v>124763694</v>
       </c>
       <c r="B15" t="n">
-        <v>92293</v>
+        <v>80057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>886701</v>
+        <v>887226</v>
       </c>
       <c r="R15" t="n">
-        <v>7405694</v>
+        <v>7405482</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763707</v>
+        <v>124763689</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886642</v>
+        <v>887395</v>
       </c>
       <c r="R16" t="n">
-        <v>7405566</v>
+        <v>7405330</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763692</v>
+        <v>124763713</v>
       </c>
       <c r="B17" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,38 +2237,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887068</v>
+        <v>887233</v>
       </c>
       <c r="R17" t="n">
-        <v>7405559</v>
+        <v>7405518</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2309,6 +2313,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2327,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763701</v>
+        <v>124763715</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887331</v>
+        <v>886673</v>
       </c>
       <c r="R18" t="n">
-        <v>7405379</v>
+        <v>7405478</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2429,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763699</v>
+        <v>124763698</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887357</v>
+        <v>887319</v>
       </c>
       <c r="R19" t="n">
-        <v>7405331</v>
+        <v>7405310</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763717</v>
+        <v>124763707</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886624</v>
+        <v>886642</v>
       </c>
       <c r="R20" t="n">
-        <v>7405597</v>
+        <v>7405566</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2607,6 +2612,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763703</v>
+        <v>124763723</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>92448</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887225</v>
+        <v>886701</v>
       </c>
       <c r="R21" t="n">
-        <v>7405332</v>
+        <v>7405694</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2735,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763690</v>
+        <v>124763719</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2757,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>886921</v>
+        <v>887305</v>
       </c>
       <c r="R22" t="n">
-        <v>7405589</v>
+        <v>7405302</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2837,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763688</v>
+        <v>124763693</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>80057</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886873</v>
+        <v>887210</v>
       </c>
       <c r="R23" t="n">
-        <v>7405551</v>
+        <v>7405471</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2913,11 +2923,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763689</v>
+        <v>124763702</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>80057</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887395</v>
+        <v>887322</v>
       </c>
       <c r="R24" t="n">
-        <v>7405330</v>
+        <v>7405379</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3020,11 +3025,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763708</v>
+        <v>124763710</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>79932</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,25 +3063,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>886733</v>
+        <v>887364</v>
       </c>
       <c r="R25" t="n">
-        <v>7405541</v>
+        <v>7405281</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3127,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763704</v>
+        <v>124763700</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887243</v>
+        <v>887330</v>
       </c>
       <c r="R26" t="n">
-        <v>7405321</v>
+        <v>7405346</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3260,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763697</v>
+        <v>124763711</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
+        <v>92484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3272,25 +3267,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887296</v>
+        <v>886862</v>
       </c>
       <c r="R27" t="n">
-        <v>7405302</v>
+        <v>7405531</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3362,10 +3357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763698</v>
+        <v>124763714</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3374,25 +3369,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3402,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887319</v>
+        <v>887236</v>
       </c>
       <c r="R28" t="n">
-        <v>7405310</v>
+        <v>7405326</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3464,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763693</v>
+        <v>124763691</v>
       </c>
       <c r="B29" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3504,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887210</v>
+        <v>887027</v>
       </c>
       <c r="R29" t="n">
-        <v>7405471</v>
+        <v>7405546</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3566,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763720</v>
+        <v>124763690</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3578,25 +3573,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887336</v>
+        <v>886921</v>
       </c>
       <c r="R30" t="n">
-        <v>7405290</v>
+        <v>7405589</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3668,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763718</v>
+        <v>124763703</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,25 +3675,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887282</v>
+        <v>887225</v>
       </c>
       <c r="R31" t="n">
-        <v>7405303</v>
+        <v>7405332</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3770,10 +3765,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763719</v>
+        <v>124763708</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,21 +3781,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887305</v>
+        <v>886733</v>
       </c>
       <c r="R32" t="n">
-        <v>7405302</v>
+        <v>7405541</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3846,6 +3841,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763713</v>
+        <v>124763720</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3884,42 +3884,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887233</v>
+        <v>887336</v>
       </c>
       <c r="R33" t="n">
-        <v>7405518</v>
+        <v>7405290</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3960,7 +3956,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3979,10 +3974,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763694</v>
+        <v>124763718</v>
       </c>
       <c r="B34" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,25 +3986,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4019,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887226</v>
+        <v>887282</v>
       </c>
       <c r="R34" t="n">
-        <v>7405482</v>
+        <v>7405303</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4081,10 +4076,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763710</v>
+        <v>124763697</v>
       </c>
       <c r="B35" t="n">
-        <v>79795</v>
+        <v>80057</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,21 +4092,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4121,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887364</v>
+        <v>887296</v>
       </c>
       <c r="R35" t="n">
-        <v>7405281</v>
+        <v>7405302</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4183,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763716</v>
+        <v>124763701</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>80057</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4195,25 +4190,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4223,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887420</v>
+        <v>887331</v>
       </c>
       <c r="R36" t="n">
-        <v>7405309</v>
+        <v>7405379</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4285,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763702</v>
+        <v>124763695</v>
       </c>
       <c r="B37" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4325,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887322</v>
+        <v>887216</v>
       </c>
       <c r="R37" t="n">
-        <v>7405379</v>
+        <v>7405484</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4387,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763691</v>
+        <v>124763716</v>
       </c>
       <c r="B38" t="n">
-        <v>79920</v>
+        <v>91184</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4399,25 +4394,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4427,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887027</v>
+        <v>887420</v>
       </c>
       <c r="R38" t="n">
-        <v>7405546</v>
+        <v>7405309</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4489,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763715</v>
+        <v>124763699</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>80057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4501,25 +4496,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4529,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>886673</v>
+        <v>887357</v>
       </c>
       <c r="R39" t="n">
-        <v>7405478</v>
+        <v>7405331</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4591,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763695</v>
+        <v>124763717</v>
       </c>
       <c r="B40" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4603,25 +4598,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887216</v>
+        <v>886624</v>
       </c>
       <c r="R40" t="n">
-        <v>7405484</v>
+        <v>7405597</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4693,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763714</v>
+        <v>124763688</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887236</v>
+        <v>886873</v>
       </c>
       <c r="R41" t="n">
-        <v>7405326</v>
+        <v>7405551</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4769,6 +4764,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4798,7 +4798,7 @@
         <v>124763712</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763700</v>
+        <v>124763722</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887330</v>
+        <v>886581</v>
       </c>
       <c r="R43" t="n">
-        <v>7405346</v>
+        <v>7405577</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763722</v>
+        <v>124763692</v>
       </c>
       <c r="B44" t="n">
-        <v>92293</v>
+        <v>80057</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>886581</v>
+        <v>887068</v>
       </c>
       <c r="R44" t="n">
-        <v>7405577</v>
+        <v>7405559</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996018</v>
+        <v>124996030</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>92448</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>887213</v>
+        <v>886961</v>
       </c>
       <c r="R8" t="n">
-        <v>7405529</v>
+        <v>7405586</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996030</v>
+        <v>124996018</v>
       </c>
       <c r="B9" t="n">
-        <v>92448</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>886961</v>
+        <v>887213</v>
       </c>
       <c r="R9" t="n">
-        <v>7405586</v>
+        <v>7405529</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763703</v>
+        <v>124763708</v>
       </c>
       <c r="B31" t="n">
-        <v>80057</v>
+        <v>57632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,25 +3675,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887225</v>
+        <v>886733</v>
       </c>
       <c r="R31" t="n">
-        <v>7405332</v>
+        <v>7405541</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3739,6 +3739,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763708</v>
+        <v>124763703</v>
       </c>
       <c r="B32" t="n">
-        <v>57632</v>
+        <v>80057</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,25 +3782,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>886733</v>
+        <v>887225</v>
       </c>
       <c r="R32" t="n">
-        <v>7405541</v>
+        <v>7405332</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3841,11 +3846,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996017</v>
+        <v>124996021</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
+        <v>80057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887402</v>
+        <v>887077</v>
       </c>
       <c r="R2" t="n">
-        <v>7405363</v>
+        <v>7405582</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996019</v>
+        <v>124996030</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>887403</v>
+        <v>886961</v>
       </c>
       <c r="R3" t="n">
-        <v>7405342</v>
+        <v>7405586</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996029</v>
+        <v>124996023</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887375</v>
+        <v>887216</v>
       </c>
       <c r="R4" t="n">
-        <v>7405296</v>
+        <v>7405474</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996024</v>
+        <v>124996027</v>
       </c>
       <c r="B5" t="n">
-        <v>80057</v>
+        <v>92484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>887153</v>
+        <v>886874</v>
       </c>
       <c r="R5" t="n">
-        <v>7405447</v>
+        <v>7405553</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996025</v>
+        <v>124996026</v>
       </c>
       <c r="B6" t="n">
         <v>80057</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887302</v>
+        <v>887216</v>
       </c>
       <c r="R6" t="n">
-        <v>7405378</v>
+        <v>7405352</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996027</v>
+        <v>124996018</v>
       </c>
       <c r="B7" t="n">
-        <v>92484</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>886874</v>
+        <v>887213</v>
       </c>
       <c r="R7" t="n">
-        <v>7405553</v>
+        <v>7405529</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996030</v>
+        <v>124996028</v>
       </c>
       <c r="B8" t="n">
-        <v>92448</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996018</v>
+        <v>124996024</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>80057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887213</v>
+        <v>887153</v>
       </c>
       <c r="R9" t="n">
-        <v>7405529</v>
+        <v>7405447</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1470,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996026</v>
+        <v>124996017</v>
       </c>
       <c r="B10" t="n">
-        <v>80057</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887216</v>
+        <v>887402</v>
       </c>
       <c r="R10" t="n">
-        <v>7405352</v>
+        <v>7405363</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996021</v>
+        <v>124996025</v>
       </c>
       <c r="B11" t="n">
         <v>80057</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887077</v>
+        <v>887302</v>
       </c>
       <c r="R11" t="n">
-        <v>7405582</v>
+        <v>7405378</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996028</v>
+        <v>124996029</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>886961</v>
+        <v>887375</v>
       </c>
       <c r="R12" t="n">
-        <v>7405586</v>
+        <v>7405296</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996023</v>
+        <v>124996019</v>
       </c>
       <c r="B13" t="n">
-        <v>80057</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887216</v>
+        <v>887403</v>
       </c>
       <c r="R13" t="n">
-        <v>7405474</v>
+        <v>7405342</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763704</v>
+        <v>124763707</v>
       </c>
       <c r="B14" t="n">
-        <v>80057</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887243</v>
+        <v>886642</v>
       </c>
       <c r="R14" t="n">
-        <v>7405321</v>
+        <v>7405566</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1990,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763694</v>
+        <v>124763691</v>
       </c>
       <c r="B15" t="n">
         <v>80057</v>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887226</v>
+        <v>887027</v>
       </c>
       <c r="R15" t="n">
-        <v>7405482</v>
+        <v>7405546</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763689</v>
+        <v>124763711</v>
       </c>
       <c r="B16" t="n">
-        <v>56836</v>
+        <v>92484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887395</v>
+        <v>886862</v>
       </c>
       <c r="R16" t="n">
-        <v>7405330</v>
+        <v>7405531</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763713</v>
+        <v>124763700</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,42 +2237,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887233</v>
+        <v>887330</v>
       </c>
       <c r="R17" t="n">
-        <v>7405518</v>
+        <v>7405346</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2313,7 +2309,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763715</v>
+        <v>124763722</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
+        <v>92448</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886673</v>
+        <v>886581</v>
       </c>
       <c r="R18" t="n">
-        <v>7405478</v>
+        <v>7405577</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2434,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763698</v>
+        <v>124763688</v>
       </c>
       <c r="B19" t="n">
-        <v>80057</v>
+        <v>56836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887319</v>
+        <v>886873</v>
       </c>
       <c r="R19" t="n">
-        <v>7405310</v>
+        <v>7405551</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2510,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763707</v>
+        <v>124763714</v>
       </c>
       <c r="B20" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>886642</v>
+        <v>887236</v>
       </c>
       <c r="R20" t="n">
-        <v>7405566</v>
+        <v>7405326</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2612,11 +2612,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763723</v>
+        <v>124763710</v>
       </c>
       <c r="B21" t="n">
-        <v>92448</v>
+        <v>79932</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>886701</v>
+        <v>887364</v>
       </c>
       <c r="R21" t="n">
-        <v>7405694</v>
+        <v>7405281</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2745,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763719</v>
+        <v>124763701</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887305</v>
+        <v>887331</v>
       </c>
       <c r="R22" t="n">
-        <v>7405302</v>
+        <v>7405379</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2847,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763693</v>
+        <v>124763699</v>
       </c>
       <c r="B23" t="n">
         <v>80057</v>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887210</v>
+        <v>887357</v>
       </c>
       <c r="R23" t="n">
-        <v>7405471</v>
+        <v>7405331</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2949,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763702</v>
+        <v>124763695</v>
       </c>
       <c r="B24" t="n">
         <v>80057</v>
@@ -2989,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887322</v>
+        <v>887216</v>
       </c>
       <c r="R24" t="n">
-        <v>7405379</v>
+        <v>7405484</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3051,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763710</v>
+        <v>124763690</v>
       </c>
       <c r="B25" t="n">
-        <v>79932</v>
+        <v>80057</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3091,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887364</v>
+        <v>886921</v>
       </c>
       <c r="R25" t="n">
-        <v>7405281</v>
+        <v>7405589</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3153,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763700</v>
+        <v>124763715</v>
       </c>
       <c r="B26" t="n">
-        <v>80057</v>
+        <v>91184</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887330</v>
+        <v>886673</v>
       </c>
       <c r="R26" t="n">
-        <v>7405346</v>
+        <v>7405478</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3255,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763711</v>
+        <v>124763716</v>
       </c>
       <c r="B27" t="n">
-        <v>92484</v>
+        <v>91184</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,21 +3266,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>886862</v>
+        <v>887420</v>
       </c>
       <c r="R27" t="n">
-        <v>7405531</v>
+        <v>7405309</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3357,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763714</v>
+        <v>124763712</v>
       </c>
       <c r="B28" t="n">
         <v>98269</v>
@@ -3397,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887236</v>
+        <v>887129</v>
       </c>
       <c r="R28" t="n">
-        <v>7405326</v>
+        <v>7405588</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3459,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763691</v>
+        <v>124763694</v>
       </c>
       <c r="B29" t="n">
         <v>80057</v>
@@ -3499,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887027</v>
+        <v>887226</v>
       </c>
       <c r="R29" t="n">
-        <v>7405546</v>
+        <v>7405482</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3561,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763690</v>
+        <v>124763719</v>
       </c>
       <c r="B30" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3573,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3601,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>886921</v>
+        <v>887305</v>
       </c>
       <c r="R30" t="n">
-        <v>7405589</v>
+        <v>7405302</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3663,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763708</v>
+        <v>124763697</v>
       </c>
       <c r="B31" t="n">
-        <v>57632</v>
+        <v>80057</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>886733</v>
+        <v>887296</v>
       </c>
       <c r="R31" t="n">
-        <v>7405541</v>
+        <v>7405302</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3739,11 +3734,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3770,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763703</v>
+        <v>124763718</v>
       </c>
       <c r="B32" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887225</v>
+        <v>887282</v>
       </c>
       <c r="R32" t="n">
-        <v>7405332</v>
+        <v>7405303</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3872,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763720</v>
+        <v>124763692</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3884,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3912,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887336</v>
+        <v>887068</v>
       </c>
       <c r="R33" t="n">
-        <v>7405290</v>
+        <v>7405559</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3974,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763718</v>
+        <v>124763713</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3986,38 +3976,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887282</v>
+        <v>887233</v>
       </c>
       <c r="R34" t="n">
-        <v>7405303</v>
+        <v>7405518</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4058,6 +4052,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4076,7 +4071,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763697</v>
+        <v>124763703</v>
       </c>
       <c r="B35" t="n">
         <v>80057</v>
@@ -4116,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887296</v>
+        <v>887225</v>
       </c>
       <c r="R35" t="n">
-        <v>7405302</v>
+        <v>7405332</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4178,10 +4173,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763701</v>
+        <v>124763717</v>
       </c>
       <c r="B36" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4190,25 +4185,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887331</v>
+        <v>886624</v>
       </c>
       <c r="R36" t="n">
-        <v>7405379</v>
+        <v>7405597</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4280,7 +4275,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763695</v>
+        <v>124763702</v>
       </c>
       <c r="B37" t="n">
         <v>80057</v>
@@ -4320,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887216</v>
+        <v>887322</v>
       </c>
       <c r="R37" t="n">
-        <v>7405484</v>
+        <v>7405379</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4382,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763716</v>
+        <v>124763689</v>
       </c>
       <c r="B38" t="n">
-        <v>91184</v>
+        <v>56836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4394,25 +4389,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4417,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887420</v>
+        <v>887395</v>
       </c>
       <c r="R38" t="n">
-        <v>7405309</v>
+        <v>7405330</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4458,6 +4453,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4484,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763699</v>
+        <v>124763723</v>
       </c>
       <c r="B39" t="n">
-        <v>80057</v>
+        <v>92448</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887357</v>
+        <v>886701</v>
       </c>
       <c r="R39" t="n">
-        <v>7405331</v>
+        <v>7405694</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763717</v>
+        <v>124763698</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,25 +4598,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>886624</v>
+        <v>887319</v>
       </c>
       <c r="R40" t="n">
-        <v>7405597</v>
+        <v>7405310</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763688</v>
+        <v>124763708</v>
       </c>
       <c r="B41" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>886873</v>
+        <v>886733</v>
       </c>
       <c r="R41" t="n">
-        <v>7405551</v>
+        <v>7405541</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4795,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763712</v>
+        <v>124763704</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,25 +4807,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887129</v>
+        <v>887243</v>
       </c>
       <c r="R42" t="n">
-        <v>7405588</v>
+        <v>7405321</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4897,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763722</v>
+        <v>124763693</v>
       </c>
       <c r="B43" t="n">
-        <v>92448</v>
+        <v>80057</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>886581</v>
+        <v>887210</v>
       </c>
       <c r="R43" t="n">
-        <v>7405577</v>
+        <v>7405471</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763692</v>
+        <v>124763720</v>
       </c>
       <c r="B44" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5011,25 +5011,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887068</v>
+        <v>887336</v>
       </c>
       <c r="R44" t="n">
-        <v>7405559</v>
+        <v>7405290</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763712</v>
+        <v>124763694</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887129</v>
+        <v>887226</v>
       </c>
       <c r="R28" t="n">
-        <v>7405588</v>
+        <v>7405482</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763694</v>
+        <v>124763719</v>
       </c>
       <c r="B29" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3466,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887226</v>
+        <v>887305</v>
       </c>
       <c r="R29" t="n">
-        <v>7405482</v>
+        <v>7405302</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763719</v>
+        <v>124763697</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887305</v>
+        <v>887296</v>
       </c>
       <c r="R30" t="n">
         <v>7405302</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763697</v>
+        <v>124763712</v>
       </c>
       <c r="B31" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887296</v>
+        <v>887129</v>
       </c>
       <c r="R31" t="n">
-        <v>7405302</v>
+        <v>7405588</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763703</v>
+        <v>124763689</v>
       </c>
       <c r="B35" t="n">
-        <v>80057</v>
+        <v>56836</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4087,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887225</v>
+        <v>887395</v>
       </c>
       <c r="R35" t="n">
-        <v>7405332</v>
+        <v>7405330</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4147,6 +4147,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4173,10 +4178,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763717</v>
+        <v>124763703</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4185,25 +4190,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4213,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>886624</v>
+        <v>887225</v>
       </c>
       <c r="R36" t="n">
-        <v>7405597</v>
+        <v>7405332</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4275,10 +4280,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763702</v>
+        <v>124763717</v>
       </c>
       <c r="B37" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,25 +4292,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4315,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887322</v>
+        <v>886624</v>
       </c>
       <c r="R37" t="n">
-        <v>7405379</v>
+        <v>7405597</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4377,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763689</v>
+        <v>124763702</v>
       </c>
       <c r="B38" t="n">
-        <v>56836</v>
+        <v>80057</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,21 +4398,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887395</v>
+        <v>887322</v>
       </c>
       <c r="R38" t="n">
-        <v>7405330</v>
+        <v>7405379</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4453,11 +4458,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4688,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763708</v>
+        <v>124763704</v>
       </c>
       <c r="B41" t="n">
-        <v>57632</v>
+        <v>80057</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>886733</v>
+        <v>887243</v>
       </c>
       <c r="R41" t="n">
-        <v>7405541</v>
+        <v>7405321</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4764,11 +4764,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4795,7 +4790,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763704</v>
+        <v>124763693</v>
       </c>
       <c r="B42" t="n">
         <v>80057</v>
@@ -4835,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887243</v>
+        <v>887210</v>
       </c>
       <c r="R42" t="n">
-        <v>7405321</v>
+        <v>7405471</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4897,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763693</v>
+        <v>124763708</v>
       </c>
       <c r="B43" t="n">
-        <v>80057</v>
+        <v>57632</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,25 +4904,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887210</v>
+        <v>886733</v>
       </c>
       <c r="R43" t="n">
-        <v>7405471</v>
+        <v>7405541</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4973,6 +4968,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996021</v>
+        <v>124996019</v>
       </c>
       <c r="B2" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887077</v>
+        <v>887403</v>
       </c>
       <c r="R2" t="n">
-        <v>7405582</v>
+        <v>7405342</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996030</v>
+        <v>124996027</v>
       </c>
       <c r="B3" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886961</v>
+        <v>886874</v>
       </c>
       <c r="R3" t="n">
-        <v>7405586</v>
+        <v>7405553</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996023</v>
+        <v>124996029</v>
       </c>
       <c r="B4" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887216</v>
+        <v>887375</v>
       </c>
       <c r="R4" t="n">
-        <v>7405474</v>
+        <v>7405296</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124996027</v>
+        <v>124996030</v>
       </c>
       <c r="B5" t="n">
-        <v>92484</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>886874</v>
+        <v>886961</v>
       </c>
       <c r="R5" t="n">
-        <v>7405553</v>
+        <v>7405586</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1088,11 +1073,6 @@
       <c r="B6" t="n">
         <v>80057</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1185,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996018</v>
+        <v>124996017</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887213</v>
+        <v>887402</v>
       </c>
       <c r="R7" t="n">
-        <v>7405529</v>
+        <v>7405363</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1261,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,11 +1267,6 @@
       <c r="B8" t="n">
         <v>98269</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1399,16 +1364,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996024</v>
+        <v>124996023</v>
       </c>
       <c r="B9" t="n">
         <v>80057</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1439,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887153</v>
+        <v>887216</v>
       </c>
       <c r="R9" t="n">
-        <v>7405447</v>
+        <v>7405474</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996017</v>
+        <v>124996025</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887402</v>
+        <v>887302</v>
       </c>
       <c r="R10" t="n">
-        <v>7405363</v>
+        <v>7405378</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,16 +1558,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996025</v>
+        <v>124996021</v>
       </c>
       <c r="B11" t="n">
         <v>80057</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1643,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887302</v>
+        <v>887077</v>
       </c>
       <c r="R11" t="n">
-        <v>7405378</v>
+        <v>7405582</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996029</v>
+        <v>124996024</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887375</v>
+        <v>887153</v>
       </c>
       <c r="R12" t="n">
-        <v>7405296</v>
+        <v>7405447</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1807,16 +1752,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996019</v>
+        <v>124996018</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1847,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887403</v>
+        <v>887213</v>
       </c>
       <c r="R13" t="n">
-        <v>7405342</v>
+        <v>7405529</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1887,7 +1827,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763707</v>
+        <v>124763718</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>886642</v>
+        <v>887282</v>
       </c>
       <c r="R14" t="n">
-        <v>7405566</v>
+        <v>7405303</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1990,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,15 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763691</v>
+        <v>124763700</v>
       </c>
       <c r="B15" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887027</v>
+        <v>887330</v>
       </c>
       <c r="R15" t="n">
-        <v>7405546</v>
+        <v>7405346</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2123,37 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763711</v>
+        <v>124763722</v>
       </c>
       <c r="B16" t="n">
-        <v>92484</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886862</v>
+        <v>886581</v>
       </c>
       <c r="R16" t="n">
-        <v>7405531</v>
+        <v>7405577</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,15 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763700</v>
+        <v>124763697</v>
       </c>
       <c r="B17" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887330</v>
+        <v>887296</v>
       </c>
       <c r="R17" t="n">
-        <v>7405346</v>
+        <v>7405302</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,37 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763722</v>
+        <v>124763708</v>
       </c>
       <c r="B18" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886581</v>
+        <v>886733</v>
       </c>
       <c r="R18" t="n">
-        <v>7405577</v>
+        <v>7405541</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2403,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,15 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763688</v>
+        <v>124763704</v>
       </c>
       <c r="B19" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>886873</v>
+        <v>887243</v>
       </c>
       <c r="R19" t="n">
-        <v>7405551</v>
+        <v>7405321</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2505,11 +2415,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,37 +2441,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763714</v>
+        <v>124763710</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887236</v>
+        <v>887364</v>
       </c>
       <c r="R20" t="n">
-        <v>7405326</v>
+        <v>7405281</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2638,37 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763710</v>
+        <v>124763711</v>
       </c>
       <c r="B21" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>887364</v>
+        <v>886862</v>
       </c>
       <c r="R21" t="n">
-        <v>7405281</v>
+        <v>7405531</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2740,15 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763701</v>
+        <v>124763702</v>
       </c>
       <c r="B22" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2670,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887331</v>
+        <v>887322</v>
       </c>
       <c r="R22" t="n">
         <v>7405379</v>
@@ -2842,37 +2732,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763699</v>
+        <v>124763717</v>
       </c>
       <c r="B23" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>887357</v>
+        <v>886624</v>
       </c>
       <c r="R23" t="n">
-        <v>7405331</v>
+        <v>7405597</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2944,15 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763695</v>
+        <v>124763690</v>
       </c>
       <c r="B24" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>887216</v>
+        <v>886921</v>
       </c>
       <c r="R24" t="n">
-        <v>7405484</v>
+        <v>7405589</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3046,37 +2926,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763690</v>
+        <v>124763712</v>
       </c>
       <c r="B25" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>886921</v>
+        <v>887129</v>
       </c>
       <c r="R25" t="n">
-        <v>7405589</v>
+        <v>7405588</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3148,37 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763715</v>
+        <v>124763694</v>
       </c>
       <c r="B26" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>886673</v>
+        <v>887226</v>
       </c>
       <c r="R26" t="n">
-        <v>7405478</v>
+        <v>7405482</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3250,37 +3120,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763716</v>
+        <v>124763703</v>
       </c>
       <c r="B27" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887420</v>
+        <v>887225</v>
       </c>
       <c r="R27" t="n">
-        <v>7405309</v>
+        <v>7405332</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3352,15 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763694</v>
+        <v>124763689</v>
       </c>
       <c r="B28" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887226</v>
+        <v>887395</v>
       </c>
       <c r="R28" t="n">
-        <v>7405482</v>
+        <v>7405330</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3428,6 +3288,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3454,15 +3319,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763719</v>
+        <v>124763707</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>887305</v>
+        <v>886642</v>
       </c>
       <c r="R29" t="n">
-        <v>7405302</v>
+        <v>7405566</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3530,6 +3390,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,15 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763697</v>
+        <v>124763723</v>
       </c>
       <c r="B30" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887296</v>
+        <v>886701</v>
       </c>
       <c r="R30" t="n">
-        <v>7405302</v>
+        <v>7405694</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3658,37 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763712</v>
+        <v>124763698</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887129</v>
+        <v>887319</v>
       </c>
       <c r="R31" t="n">
-        <v>7405588</v>
+        <v>7405310</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3760,37 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763718</v>
+        <v>124763701</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887282</v>
+        <v>887331</v>
       </c>
       <c r="R32" t="n">
-        <v>7405303</v>
+        <v>7405379</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3862,37 +3712,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763692</v>
+        <v>124763719</v>
       </c>
       <c r="B33" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887068</v>
+        <v>887305</v>
       </c>
       <c r="R33" t="n">
-        <v>7405559</v>
+        <v>7405302</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3964,54 +3809,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763713</v>
+        <v>124763695</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887233</v>
+        <v>887216</v>
       </c>
       <c r="R34" t="n">
-        <v>7405518</v>
+        <v>7405484</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4052,7 +3888,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4071,37 +3906,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763689</v>
+        <v>124763715</v>
       </c>
       <c r="B35" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>887395</v>
+        <v>886673</v>
       </c>
       <c r="R35" t="n">
-        <v>7405330</v>
+        <v>7405478</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4147,11 +3977,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4178,15 +4003,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763703</v>
+        <v>124763692</v>
       </c>
       <c r="B36" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,10 +4038,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887225</v>
+        <v>887068</v>
       </c>
       <c r="R36" t="n">
-        <v>7405332</v>
+        <v>7405559</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4280,37 +4100,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763717</v>
+        <v>124763699</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,10 +4135,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>886624</v>
+        <v>887357</v>
       </c>
       <c r="R37" t="n">
-        <v>7405597</v>
+        <v>7405331</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4382,37 +4197,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763702</v>
+        <v>124763716</v>
       </c>
       <c r="B38" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4232,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887322</v>
+        <v>887420</v>
       </c>
       <c r="R38" t="n">
-        <v>7405379</v>
+        <v>7405309</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4484,15 +4294,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763723</v>
+        <v>124763691</v>
       </c>
       <c r="B39" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4500,21 +4305,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4329,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>886701</v>
+        <v>887027</v>
       </c>
       <c r="R39" t="n">
-        <v>7405694</v>
+        <v>7405546</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4586,15 +4391,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763698</v>
+        <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,21 +4402,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4426,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>887319</v>
+        <v>886873</v>
       </c>
       <c r="R40" t="n">
-        <v>7405310</v>
+        <v>7405551</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4662,6 +4462,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4688,50 +4493,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763704</v>
+        <v>124763713</v>
       </c>
       <c r="B41" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887243</v>
+        <v>887233</v>
       </c>
       <c r="R41" t="n">
-        <v>7405321</v>
+        <v>7405518</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4772,6 +4576,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4793,12 +4598,7 @@
         <v>124763693</v>
       </c>
       <c r="B42" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4892,15 +4692,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763708</v>
+        <v>124763720</v>
       </c>
       <c r="B43" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4908,21 +4703,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,10 +4727,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>886733</v>
+        <v>887336</v>
       </c>
       <c r="R43" t="n">
-        <v>7405541</v>
+        <v>7405290</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4968,11 +4763,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4999,37 +4789,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763720</v>
+        <v>124763714</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +4824,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887336</v>
+        <v>887236</v>
       </c>
       <c r="R44" t="n">
-        <v>7405290</v>
+        <v>7405326</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763718</v>
+        <v>124763722</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>92502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887282</v>
+        <v>886581</v>
       </c>
       <c r="R14" t="n">
-        <v>7405303</v>
+        <v>7405577</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763700</v>
+        <v>124763718</v>
       </c>
       <c r="B15" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887330</v>
+        <v>887282</v>
       </c>
       <c r="R15" t="n">
-        <v>7405346</v>
+        <v>7405303</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763722</v>
+        <v>124763700</v>
       </c>
       <c r="B16" t="n">
-        <v>92502</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886581</v>
+        <v>887330</v>
       </c>
       <c r="R16" t="n">
-        <v>7405577</v>
+        <v>7405346</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763722</v>
+        <v>124763700</v>
       </c>
       <c r="B14" t="n">
-        <v>92502</v>
+        <v>80099</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>886581</v>
+        <v>887330</v>
       </c>
       <c r="R14" t="n">
-        <v>7405577</v>
+        <v>7405346</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763700</v>
+        <v>124763722</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>92509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>887330</v>
+        <v>886581</v>
       </c>
       <c r="R16" t="n">
-        <v>7405346</v>
+        <v>7405577</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2242,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763708</v>
+        <v>124763704</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>80099</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>886733</v>
+        <v>887243</v>
       </c>
       <c r="R18" t="n">
-        <v>7405541</v>
+        <v>7405321</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2313,11 +2313,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,32 +2339,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763704</v>
+        <v>124763708</v>
       </c>
       <c r="B19" t="n">
-        <v>80099</v>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>887243</v>
+        <v>886733</v>
       </c>
       <c r="R19" t="n">
-        <v>7405321</v>
+        <v>7405541</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2415,6 +2410,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763711</v>
+        <v>124763717</v>
       </c>
       <c r="B21" t="n">
-        <v>92538</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>886862</v>
+        <v>886624</v>
       </c>
       <c r="R21" t="n">
-        <v>7405531</v>
+        <v>7405597</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763717</v>
+        <v>124763711</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>92545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886624</v>
+        <v>886862</v>
       </c>
       <c r="R23" t="n">
-        <v>7405597</v>
+        <v>7405531</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2929,7 +2929,7 @@
         <v>124763712</v>
       </c>
       <c r="B25" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3319,32 +3319,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763707</v>
+        <v>124763723</v>
       </c>
       <c r="B29" t="n">
-        <v>57648</v>
+        <v>92509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886642</v>
+        <v>886701</v>
       </c>
       <c r="R29" t="n">
-        <v>7405566</v>
+        <v>7405694</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3390,11 +3390,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3421,10 +3416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763723</v>
+        <v>124763698</v>
       </c>
       <c r="B30" t="n">
-        <v>92502</v>
+        <v>80099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3427,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>886701</v>
+        <v>887319</v>
       </c>
       <c r="R30" t="n">
-        <v>7405694</v>
+        <v>7405310</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3518,32 +3513,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763698</v>
+        <v>124763707</v>
       </c>
       <c r="B31" t="n">
-        <v>80099</v>
+        <v>57648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>887319</v>
+        <v>886642</v>
       </c>
       <c r="R31" t="n">
-        <v>7405310</v>
+        <v>7405566</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3589,6 +3584,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3809,32 +3809,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763695</v>
+        <v>124763715</v>
       </c>
       <c r="B34" t="n">
-        <v>80099</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>887216</v>
+        <v>886673</v>
       </c>
       <c r="R34" t="n">
-        <v>7405484</v>
+        <v>7405478</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3906,32 +3906,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763715</v>
+        <v>124763695</v>
       </c>
       <c r="B35" t="n">
-        <v>91238</v>
+        <v>80099</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>886673</v>
+        <v>887216</v>
       </c>
       <c r="R35" t="n">
-        <v>7405478</v>
+        <v>7405484</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4200,7 +4200,7 @@
         <v>124763716</v>
       </c>
       <c r="B38" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>124763713</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4595,32 +4595,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763693</v>
+        <v>124763720</v>
       </c>
       <c r="B42" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887210</v>
+        <v>887336</v>
       </c>
       <c r="R42" t="n">
-        <v>7405471</v>
+        <v>7405290</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4692,32 +4692,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763720</v>
+        <v>124763693</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>80099</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887336</v>
+        <v>887210</v>
       </c>
       <c r="R43" t="n">
-        <v>7405290</v>
+        <v>7405471</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4792,7 +4792,7 @@
         <v>124763714</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>124763689</v>
       </c>
       <c r="B28" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>124763689</v>
       </c>
       <c r="B28" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>124763689</v>
       </c>
       <c r="B28" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>124763689</v>
       </c>
       <c r="B28" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>124763688</v>
       </c>
       <c r="B40" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124996019</v>
+        <v>124763722</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>887403</v>
+        <v>886581</v>
       </c>
       <c r="R2" t="n">
-        <v>7405342</v>
+        <v>7405577</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,11 +748,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124996027</v>
+        <v>124763723</v>
       </c>
       <c r="B3" t="n">
-        <v>92484</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>886874</v>
+        <v>886701</v>
       </c>
       <c r="R3" t="n">
-        <v>7405553</v>
+        <v>7405694</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124996029</v>
+        <v>124763724</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>887375</v>
+        <v>886738</v>
       </c>
       <c r="R4" t="n">
-        <v>7405296</v>
+        <v>7405685</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -974,11 +969,11 @@
         <v>124996030</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124996026</v>
+        <v>124996017</v>
       </c>
       <c r="B6" t="n">
-        <v>80057</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>887216</v>
+        <v>887402</v>
       </c>
       <c r="R6" t="n">
-        <v>7405352</v>
+        <v>7405363</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1165,45 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124996017</v>
+        <v>124763711</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>887402</v>
+        <v>886862</v>
       </c>
       <c r="R7" t="n">
-        <v>7405363</v>
+        <v>7405531</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1250,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124996028</v>
+        <v>124996027</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>886961</v>
+        <v>886874</v>
       </c>
       <c r="R8" t="n">
-        <v>7405586</v>
+        <v>7405553</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1333,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>O,5 m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124996023</v>
+        <v>124763717</v>
       </c>
       <c r="B9" t="n">
-        <v>80057</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>887216</v>
+        <v>886624</v>
       </c>
       <c r="R9" t="n">
-        <v>7405474</v>
+        <v>7405597</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1449,57 +1439,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124996025</v>
+        <v>124763718</v>
       </c>
       <c r="B10" t="n">
-        <v>80057</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>887302</v>
+        <v>887282</v>
       </c>
       <c r="R10" t="n">
-        <v>7405378</v>
+        <v>7405303</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1546,57 +1536,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124996021</v>
+        <v>124763719</v>
       </c>
       <c r="B11" t="n">
-        <v>80057</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>887077</v>
+        <v>887305</v>
       </c>
       <c r="R11" t="n">
-        <v>7405582</v>
+        <v>7405302</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1643,57 +1633,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124996024</v>
+        <v>124763720</v>
       </c>
       <c r="B12" t="n">
-        <v>80057</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>887153</v>
+        <v>887336</v>
       </c>
       <c r="R12" t="n">
-        <v>7405447</v>
+        <v>7405290</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1740,57 +1730,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124996018</v>
+        <v>124763721</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Outinenvaara, Nb</t>
+          <t>Outisenvaara, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>887213</v>
+        <v>887230</v>
       </c>
       <c r="R13" t="n">
-        <v>7405529</v>
+        <v>7405312</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1825,11 +1815,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1842,57 +1827,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124763700</v>
+        <v>124996029</v>
       </c>
       <c r="B14" t="n">
-        <v>80099</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>887330</v>
+        <v>887375</v>
       </c>
       <c r="R14" t="n">
-        <v>7405346</v>
+        <v>7405296</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1939,44 +1924,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124763718</v>
+        <v>124763710</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>887282</v>
+        <v>887364</v>
       </c>
       <c r="R15" t="n">
-        <v>7405303</v>
+        <v>7405281</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2048,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124763722</v>
+        <v>124763690</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>886581</v>
+        <v>886921</v>
       </c>
       <c r="R16" t="n">
-        <v>7405577</v>
+        <v>7405589</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2145,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124763697</v>
+        <v>124763691</v>
       </c>
       <c r="B17" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2180,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>887296</v>
+        <v>887027</v>
       </c>
       <c r="R17" t="n">
-        <v>7405302</v>
+        <v>7405546</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2242,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124763704</v>
+        <v>124763692</v>
       </c>
       <c r="B18" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>887243</v>
+        <v>887068</v>
       </c>
       <c r="R18" t="n">
-        <v>7405321</v>
+        <v>7405559</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2339,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124763708</v>
+        <v>124763693</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>886733</v>
+        <v>887210</v>
       </c>
       <c r="R19" t="n">
-        <v>7405541</v>
+        <v>7405471</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2410,11 +2395,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2441,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124763710</v>
+        <v>124763694</v>
       </c>
       <c r="B20" t="n">
-        <v>79974</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>887364</v>
+        <v>887226</v>
       </c>
       <c r="R20" t="n">
-        <v>7405281</v>
+        <v>7405482</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2538,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124763717</v>
+        <v>124763695</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>886624</v>
+        <v>887216</v>
       </c>
       <c r="R21" t="n">
-        <v>7405597</v>
+        <v>7405484</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2635,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124763702</v>
+        <v>124763696</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>887322</v>
+        <v>887257</v>
       </c>
       <c r="R22" t="n">
-        <v>7405379</v>
+        <v>7405292</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2732,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124763711</v>
+        <v>124763697</v>
       </c>
       <c r="B23" t="n">
-        <v>92545</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>886862</v>
+        <v>887296</v>
       </c>
       <c r="R23" t="n">
-        <v>7405531</v>
+        <v>7405302</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2829,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124763690</v>
+        <v>124763698</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2864,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>886921</v>
+        <v>887319</v>
       </c>
       <c r="R24" t="n">
-        <v>7405589</v>
+        <v>7405310</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -2926,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124763712</v>
+        <v>124763699</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2961,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>887129</v>
+        <v>887357</v>
       </c>
       <c r="R25" t="n">
-        <v>7405588</v>
+        <v>7405331</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3023,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124763694</v>
+        <v>124763700</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>887226</v>
+        <v>887330</v>
       </c>
       <c r="R26" t="n">
-        <v>7405482</v>
+        <v>7405346</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3120,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124763703</v>
+        <v>124763701</v>
       </c>
       <c r="B27" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3155,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>887225</v>
+        <v>887331</v>
       </c>
       <c r="R27" t="n">
-        <v>7405332</v>
+        <v>7405379</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3217,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124763689</v>
+        <v>124763702</v>
       </c>
       <c r="B28" t="n">
-        <v>57053</v>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3252,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>887395</v>
+        <v>887322</v>
       </c>
       <c r="R28" t="n">
-        <v>7405330</v>
+        <v>7405379</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3288,11 +3268,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3319,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124763723</v>
+        <v>124763703</v>
       </c>
       <c r="B29" t="n">
-        <v>92509</v>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3330,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3354,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>886701</v>
+        <v>887225</v>
       </c>
       <c r="R29" t="n">
-        <v>7405694</v>
+        <v>7405332</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3416,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124763698</v>
+        <v>124763704</v>
       </c>
       <c r="B30" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3451,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>887319</v>
+        <v>887243</v>
       </c>
       <c r="R30" t="n">
-        <v>7405310</v>
+        <v>7405321</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3513,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124763707</v>
+        <v>124763705</v>
       </c>
       <c r="B31" t="n">
-        <v>57648</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3548,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>886642</v>
+        <v>887226</v>
       </c>
       <c r="R31" t="n">
-        <v>7405566</v>
+        <v>7405320</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3584,11 +3559,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3615,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124763701</v>
+        <v>124763706</v>
       </c>
       <c r="B32" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3650,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>887331</v>
+        <v>887218</v>
       </c>
       <c r="R32" t="n">
-        <v>7405379</v>
+        <v>7405314</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3712,45 +3682,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124763719</v>
+        <v>124996021</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>887305</v>
+        <v>887077</v>
       </c>
       <c r="R33" t="n">
-        <v>7405302</v>
+        <v>7405582</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -3797,57 +3767,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124763715</v>
+        <v>124996022</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>886673</v>
+        <v>887229</v>
       </c>
       <c r="R34" t="n">
-        <v>7405478</v>
+        <v>7405319</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3894,22 +3864,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124763695</v>
+        <v>124996023</v>
       </c>
       <c r="B35" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3937,14 +3907,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
         <v>887216</v>
       </c>
       <c r="R35" t="n">
-        <v>7405484</v>
+        <v>7405474</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -3991,22 +3961,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124763692</v>
+        <v>124996024</v>
       </c>
       <c r="B36" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4034,14 +4004,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>887068</v>
+        <v>887153</v>
       </c>
       <c r="R36" t="n">
-        <v>7405559</v>
+        <v>7405447</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4088,22 +4058,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124763699</v>
+        <v>124996025</v>
       </c>
       <c r="B37" t="n">
-        <v>80099</v>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4131,14 +4101,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>887357</v>
+        <v>887302</v>
       </c>
       <c r="R37" t="n">
-        <v>7405331</v>
+        <v>7405378</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4185,57 +4155,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124763716</v>
+        <v>124996026</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>887420</v>
+        <v>887216</v>
       </c>
       <c r="R38" t="n">
-        <v>7405309</v>
+        <v>7405352</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4282,22 +4252,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124763691</v>
+        <v>124763707</v>
       </c>
       <c r="B39" t="n">
-        <v>80099</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4305,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4329,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>887027</v>
+        <v>886642</v>
       </c>
       <c r="R39" t="n">
-        <v>7405546</v>
+        <v>7405566</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4365,6 +4335,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4391,10 +4366,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124763688</v>
+        <v>124763708</v>
       </c>
       <c r="B40" t="n">
-        <v>57053</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4402,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4426,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>886873</v>
+        <v>886733</v>
       </c>
       <c r="R40" t="n">
-        <v>7405551</v>
+        <v>7405541</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4466,7 +4441,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkat</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4493,49 +4468,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124763713</v>
+        <v>124996018</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>887233</v>
+        <v>887213</v>
       </c>
       <c r="R41" t="n">
-        <v>7405518</v>
+        <v>7405529</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4570,35 +4541,39 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124763720</v>
+        <v>124996019</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4606,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Outisenvaara, Nb</t>
+          <t>Outinenvaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>887336</v>
+        <v>887403</v>
       </c>
       <c r="R42" t="n">
-        <v>7405290</v>
+        <v>7405342</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -4668,6 +4643,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4680,22 +4660,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124763693</v>
+        <v>124763687</v>
       </c>
       <c r="B43" t="n">
-        <v>80099</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4703,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4727,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>887210</v>
+        <v>886714</v>
       </c>
       <c r="R43" t="n">
-        <v>7405471</v>
+        <v>7405387</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -4763,6 +4743,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4789,32 +4774,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124763714</v>
+        <v>124763688</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4824,10 +4809,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>887236</v>
+        <v>886873</v>
       </c>
       <c r="R44" t="n">
-        <v>7405326</v>
+        <v>7405551</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -4862,6 +4847,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4883,6 +4873,506 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124763689</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>887395</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7405330</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124763712</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>887129</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7405588</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124763713</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>887233</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7405518</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124763714</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Outisenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>887236</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7405326</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124996028</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Outinenvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>886961</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7405586</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>O,5 m2</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12004-2022 artfynd.xlsx
+++ b/artfynd/A 12004-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763722</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763724</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996030</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763711</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996027</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763718</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763719</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763720</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763721</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996029</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763710</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763690</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763691</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763692</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763693</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763694</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763695</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763696</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763697</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763698</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763699</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763700</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763701</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763702</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763703</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763704</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763705</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763706</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996021</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996022</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996023</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996024</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763707</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4465,6 +4660,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763708</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4567,6 +4767,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996018</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4669,6 +4874,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996019</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4771,6 +4981,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763687</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4873,6 +5088,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763688</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4975,6 +5195,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763689</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5072,6 +5297,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763712</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5174,6 +5404,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763713</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5271,6 +5506,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124763714</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5373,8 +5613,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124996028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>